--- a/output/ATI_liquidity_assessment.xlsx
+++ b/output/ATI_liquidity_assessment.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата отчёта: 2026-07-21 16:10 | Источники: ТАЗ ORDERS, ТУЗ (группы запросов), EXPENDABLES, АТИ</t>
+          <t>Дата отчёта: 2026-07-21 16:25 | Источники: ТАЗ ORDERS, ТУЗ (группы запросов), EXPENDABLES, АТИ</t>
         </is>
       </c>
     </row>
@@ -916,33 +916,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>• Колонки ATA и S/N убраны; запросы ТУЗ и EXP объединены в один столбец.</t>
+          <t>• Исправлено чтение ТУЗ: учтён сдвиг колонок (Sales/Purch ID) и сохранение всех Offered по квотам одного RFQ.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>• Сопоставление P/N: регистр, пробелы, тире; soft-ключ и ALT P/N.</t>
+          <t>• Колонки ATA и S/N убраны; запросы ТУЗ и EXP объединены в один столбец.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>• Цена ориентир только из «Продажная, ед.» / «Offered per unit $» / «Sell Price EA».</t>
+          <t>• Сопоставление P/N: регистр, пробелы, тире; soft-ключ и ALT P/N.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>• Цена ориентир только из «Продажная, ед.» / «Offered per unit $» / «Sell Price EA».</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>• «Закупка на склад» не считается рыночным клиентом.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A37:F37"/>
     <mergeCell ref="A27:F27"/>
@@ -963,6 +970,7 @@
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -986,7 +994,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
@@ -1141,12 +1149,12 @@
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 4 · клиенты: ЮВТ, Руслайн (2 уник.) | Запросы ТУЗ+EXP: 4 · клиенты: Аллюр Сервис, Русджет, ЮВТ, Аэрофлот Техникс (4 уник.)</t>
+          <t>Заказы ТАЗ: 4 · клиенты: Руслайн, ЮВТ (2 уник.) | Запросы ТУЗ+EXP: 4 · клиенты: Русджет, ЮВТ, Аэрофлот Техникс, Аллюр Сервис (4 уник.)</t>
         </is>
       </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — ЮВТ, Руслайн, qty≈142); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Аллюр Сервис, Русджет, ЮВТ, Аэрофлот Техникс, qty≈29). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $5.00: медиана продажных цен ТАЗ (все даты) (n=3, min $4.50, max $12.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — Руслайн, ЮВТ, qty≈142); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Русджет, ЮВТ, Аэрофлот Техникс, Аллюр Сервис, qty≈29). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $5.00: медиана продажных цен ТАЗ (все даты) (n=3, min $4.50, max $12.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1302,12 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 6 · клиенты: Ямал, Аэрофлот, S7 Engineering, Уральские Авиалинии (5 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 6 · клиенты: S7 Engineering, Уральские Авиалинии, Аэрофлот, UTG (5 уник.)</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈37); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — Ямал, Аэрофлот, S7 Engineering, Уральские Авиалинии, UTG, qty≈246.2). Сопоставление: ALT P/N, точное P/N. На складе: 8 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $9.00: медиана продажных цен ТАЗ (все даты) (n=1, min $9.00, max $9.00, последний заказ 2024-09-10). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (679 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈37); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — S7 Engineering, Уральские Авиалинии, Аэрофлот, UTG, Ямал, qty≈293.5). Сопоставление: ALT P/N, точное P/N. На складе: 8 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $9.00: медиана продажных цен ТАЗ (все даты) (n=1, min $9.00, max $9.00, последний заказ 2024-09-10). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (679 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1455,12 @@
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 11 · клиенты: Смартавиа, Nordwind, Utair, СмартАвиа (6 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 11 · клиенты: S7 Engineering, Смартавиа, Nordwind, Utair (6 уник.)</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 11 (уник. P/N+клиент+день; клиентов: 6 — Смартавиа, Nordwind, Utair, СмартАвиа, Якутия, qty≈29). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 11 (уник. P/N+клиент+день; клиентов: 6 — S7 Engineering, Смартавиа, Nordwind, Utair, СмартАвиа, qty≈27.3636). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1557,12 @@
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 14 · клиенты: S7 Engineering, Аэрофлот, Utair, Аэрофлот Техникс (7 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 14 · клиенты: Utair, Аэрофлот Техникс, Nordwind, Уральские Авиалинии (7 уник.)</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 14 (уник. P/N+клиент+день; клиентов: 7 — S7 Engineering, Аэрофлот, Utair, Аэрофлот Техникс, Nordwind, qty≈435). Сопоставление: ALT P/N, точное P/N. На складе: 13 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $41.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=7, min $36.00, max $49.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-24.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 14 (уник. P/N+клиент+день; клиентов: 7 — Utair, Аэрофлот Техникс, Nordwind, Уральские Авиалинии, Аэрофлот, qty≈435). Сопоставление: ALT P/N, точное P/N. На складе: 13 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $41.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=7, min $36.00, max $49.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-24.</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1710,12 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 3 · клиенты: Jetica, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: Jetica, Дримджет, ЮВТ, Без клиента (4 уник.)</t>
+          <t>Заказы ТАЗ: 3 · клиенты: Jetica, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: ЮВТ, Jetica, Дримджет, Без клиента (4 уник.)</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 3 (уник. №заказа+P/N; клиентов: 2 — Jetica, Дримджет, qty≈3); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — Jetica, Дримджет, ЮВТ, Без клиента, qty≈5). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,400.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $16,400.00, max $16,400.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-04-10).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 3 (уник. №заказа+P/N; клиентов: 2 — Jetica, Дримджет, qty≈3); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Jetica, Дримджет, Без клиента, qty≈6.25). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,400.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $16,400.00, max $16,400.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-04-10).</t>
         </is>
       </c>
     </row>
@@ -2365,12 +2373,12 @@
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: ЮВТ, Ямал, Скай Партнер, Руслайн (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: Руслайн, ЮВТ, Ямал, Скай Партнер (4 уник.)</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Ямал, Скай Партнер, Руслайн, qty≈14). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $11,500.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=13, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 4 — Руслайн, ЮВТ, Ямал, Скай Партнер, qty≈14). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $11,500.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=13, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -2569,12 +2577,12 @@
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Северсталь | Запросы ТУЗ+EXP: 4 · клиенты: ЮВТ, Тулпар Техник, Северсталь (3 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Северсталь | Запросы ТУЗ+EXP: 4 · клиенты: Тулпар Техник, Северсталь, ЮВТ (3 уник.)</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Северсталь, qty≈1); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, Тулпар Техник, Северсталь, qty≈22). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $650.00: медиана продажных цен ТАЗ (все даты) (n=1, min $650.00, max $650.00, последний заказ 2024-11-06). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (622 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Северсталь, qty≈1); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — Тулпар Техник, Северсталь, ЮВТ, qty≈22). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $650.00: медиана продажных цен ТАЗ (все даты) (n=1, min $650.00, max $650.00, последний заказ 2024-11-06). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (622 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2781,12 @@
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Jetica | Запросы ТУЗ+EXP: 4 · клиенты: Ираэро, ЮВТ, Jetica (3 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Jetica | Запросы ТУЗ+EXP: 4 · клиенты: ЮВТ, Jetica, Ираэро (3 уник.)</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Jetica, qty≈1); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — Ираэро, ЮВТ, Jetica, qty≈5). Сопоставление: ALT P/N, точное P/N. На складе: 26 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $630.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $630.00, max $630.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Jetica, qty≈1); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, Jetica, Ираэро, qty≈5). Сопоставление: ALT P/N, точное P/N. На складе: 26 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $630.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $630.00, max $630.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
         </is>
       </c>
     </row>
@@ -4558,12 +4566,12 @@
       </c>
       <c r="J70" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: Аллюр Сервис, АК Тулпар, АК Тулпар (Джет Экспресс) (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: АК Тулпар (Джет Экспресс), Аллюр Сервис, АК Тулпар (3 уник.)</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Аллюр Сервис, АК Тулпар, АК Тулпар (Джет Экспресс), qty≈3). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: OVERHAULED. Ориентир $5,700.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $5,700.00, max $5,700.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-04-14.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — АК Тулпар (Джет Экспресс), Аллюр Сервис, АК Тулпар, qty≈3). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: OVERHAULED. Ориентир $5,700.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $5,700.00, max $5,700.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-04-14.</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5159,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
@@ -5306,12 +5314,12 @@
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 6 · клиенты: Ямал, Аэрофлот, S7 Engineering, Уральские Авиалинии (5 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 6 · клиенты: S7 Engineering, Уральские Авиалинии, Аэрофлот, UTG (5 уник.)</t>
         </is>
       </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈37); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — Ямал, Аэрофлот, S7 Engineering, Уральские Авиалинии, UTG, qty≈246.2). Сопоставление: ALT P/N, точное P/N. На складе: 8 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $9.00: медиана продажных цен ТАЗ (все даты) (n=1, min $9.00, max $9.00, последний заказ 2024-09-10). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (679 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈37); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — S7 Engineering, Уральские Авиалинии, Аэрофлот, UTG, Ямал, qty≈293.5). Сопоставление: ALT P/N, точное P/N. На складе: 8 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $9.00: медиана продажных цен ТАЗ (все даты) (n=1, min $9.00, max $9.00, последний заказ 2024-09-10). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (679 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -5408,12 +5416,12 @@
       </c>
       <c r="J5" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 11 · клиенты: Смартавиа, Nordwind, Utair, СмартАвиа (6 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 11 · клиенты: S7 Engineering, Смартавиа, Nordwind, Utair (6 уник.)</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 11 (уник. P/N+клиент+день; клиентов: 6 — Смартавиа, Nordwind, Utair, СмартАвиа, Якутия, qty≈29). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 11 (уник. P/N+клиент+день; клиентов: 6 — S7 Engineering, Смартавиа, Nordwind, Utair, СмартАвиа, qty≈27.3636). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -6878,9 +6886,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
@@ -7335,9 +7343,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J43" s="13" t="inlineStr">
@@ -7537,9 +7545,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J47" s="13" t="inlineStr">
@@ -7841,9 +7849,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J53" s="13" t="inlineStr">
@@ -7941,9 +7949,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J55" s="13" t="inlineStr">
@@ -7990,9 +7998,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
@@ -15232,7 +15240,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
@@ -15387,12 +15395,12 @@
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 3 · клиенты: Jetica, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: Jetica, Дримджет, ЮВТ, Без клиента (4 уник.)</t>
+          <t>Заказы ТАЗ: 3 · клиенты: Jetica, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: ЮВТ, Jetica, Дримджет, Без клиента (4 уник.)</t>
         </is>
       </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 3 (уник. №заказа+P/N; клиентов: 2 — Jetica, Дримджет, qty≈3); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — Jetica, Дримджет, ЮВТ, Без клиента, qty≈5). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,400.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $16,400.00, max $16,400.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-04-10).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 3 (уник. №заказа+P/N; клиентов: 2 — Jetica, Дримджет, qty≈3); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Jetica, Дримджет, Без клиента, qty≈6.25). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,400.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $16,400.00, max $16,400.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-04-10).</t>
         </is>
       </c>
     </row>
@@ -16101,12 +16109,12 @@
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Ираэро, Руслайн (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Руслайн, Ираэро (2 уник.)</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 2 — Ираэро, Руслайн, qty≈4). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,100.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $10,500.00, max $19,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-09.</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 2 — Руслайн, Ираэро, qty≈4). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,100.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $10,500.00, max $19,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-09.</t>
         </is>
       </c>
     </row>
@@ -16347,9 +16355,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
@@ -16396,9 +16404,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr">
@@ -16598,9 +16606,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J27" s="13" t="inlineStr">
@@ -16647,9 +16655,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
@@ -16696,9 +16704,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J29" s="13" t="inlineStr">
@@ -16898,9 +16906,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J33" s="13" t="inlineStr">
@@ -18507,7 +18515,7 @@
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
     <col width="48" customWidth="1" min="10" max="10"/>
     <col width="80" customWidth="1" min="11" max="11"/>
   </cols>
@@ -18662,12 +18670,12 @@
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 4 · клиенты: ЮВТ, Руслайн (2 уник.) | Запросы ТУЗ+EXP: 4 · клиенты: Аллюр Сервис, Русджет, ЮВТ, Аэрофлот Техникс (4 уник.)</t>
+          <t>Заказы ТАЗ: 4 · клиенты: Руслайн, ЮВТ (2 уник.) | Запросы ТУЗ+EXP: 4 · клиенты: Русджет, ЮВТ, Аэрофлот Техникс, Аллюр Сервис (4 уник.)</t>
         </is>
       </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — ЮВТ, Руслайн, qty≈142); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Аллюр Сервис, Русджет, ЮВТ, Аэрофлот Техникс, qty≈29). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $5.00: медиана продажных цен ТАЗ (все даты) (n=3, min $4.50, max $12.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — Руслайн, ЮВТ, qty≈142); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Русджет, ЮВТ, Аэрофлот Техникс, Аллюр Сервис, qty≈29). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $5.00: медиана продажных цен ТАЗ (все даты) (n=3, min $4.50, max $12.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -18917,12 +18925,12 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 14 · клиенты: S7 Engineering, Аэрофлот, Utair, Аэрофлот Техникс (7 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 14 · клиенты: Utair, Аэрофлот Техникс, Nordwind, Уральские Авиалинии (7 уник.)</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 14 (уник. P/N+клиент+день; клиентов: 7 — S7 Engineering, Аэрофлот, Utair, Аэрофлот Техникс, Nordwind, qty≈435). Сопоставление: ALT P/N, точное P/N. На складе: 13 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $41.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=7, min $36.00, max $49.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-24.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 14 (уник. P/N+клиент+день; клиентов: 7 — Utair, Аэрофлот Техникс, Nordwind, Уральские Авиалинии, Аэрофлот, qty≈435). Сопоставление: ALT P/N, точное P/N. На складе: 13 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $41.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=7, min $36.00, max $49.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-24.</t>
         </is>
       </c>
     </row>
@@ -19019,12 +19027,12 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 3 · клиенты: Jetica, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: Jetica, Дримджет, ЮВТ, Без клиента (4 уник.)</t>
+          <t>Заказы ТАЗ: 3 · клиенты: Jetica, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: ЮВТ, Jetica, Дримджет, Без клиента (4 уник.)</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 3 (уник. №заказа+P/N; клиентов: 2 — Jetica, Дримджет, qty≈3); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — Jetica, Дримджет, ЮВТ, Без клиента, qty≈5). Сопоставление: ALT P/N, точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $16,400.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $16,400.00, max $16,400.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-04-10).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 3 (уник. №заказа+P/N; клиентов: 2 — Jetica, Дримджет, qty≈3); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Jetica, Дримджет, Без клиента, qty≈6.25). Сопоставление: ALT P/N, точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $16,400.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $16,400.00, max $16,400.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-04-10).</t>
         </is>
       </c>
     </row>
@@ -19427,12 +19435,12 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: ЮВТ, Ямал, Скай Партнер, Руслайн (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: Руслайн, ЮВТ, Ямал, Скай Партнер (4 уник.)</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Ямал, Скай Партнер, Руслайн, qty≈14). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $11,500.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=13, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 4 — Руслайн, ЮВТ, Ямал, Скай Партнер, qty≈14). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $11,500.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=13, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -19631,12 +19639,12 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Северсталь | Запросы ТУЗ+EXP: 4 · клиенты: ЮВТ, Тулпар Техник, Северсталь (3 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Северсталь | Запросы ТУЗ+EXP: 4 · клиенты: Тулпар Техник, Северсталь, ЮВТ (3 уник.)</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Северсталь, qty≈1); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, Тулпар Техник, Северсталь, qty≈22). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $650.00: медиана продажных цен ТАЗ (все даты) (n=1, min $650.00, max $650.00, последний заказ 2024-11-06). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (622 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Северсталь, qty≈1); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — Тулпар Техник, Северсталь, ЮВТ, qty≈22). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $650.00: медиана продажных цен ТАЗ (все даты) (n=1, min $650.00, max $650.00, последний заказ 2024-11-06). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (622 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -19784,12 +19792,12 @@
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Jetica | Запросы ТУЗ+EXP: 4 · клиенты: Ираэро, ЮВТ, Jetica (3 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Jetica | Запросы ТУЗ+EXP: 4 · клиенты: ЮВТ, Jetica, Ираэро (3 уник.)</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Jetica, qty≈1); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — Ираэро, ЮВТ, Jetica, qty≈5). Сопоставление: ALT P/N, точное P/N. На складе: 26 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $630.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $630.00, max $630.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Jetica, qty≈1); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, Jetica, Ираэро, qty≈5). Сопоставление: ALT P/N, точное P/N. На складе: 26 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $630.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $630.00, max $630.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
         </is>
       </c>
     </row>
@@ -21314,12 +21322,12 @@
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: Аллюр Сервис, АК Тулпар, АК Тулпар (Джет Экспресс) (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: АК Тулпар (Джет Экспресс), Аллюр Сервис, АК Тулпар (3 уник.)</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Аллюр Сервис, АК Тулпар, АК Тулпар (Джет Экспресс), qty≈3). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: OVERHAULED. Ориентир $5,700.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $5,700.00, max $5,700.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-04-14.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — АК Тулпар (Джет Экспресс), Аллюр Сервис, АК Тулпар, qty≈3). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: OVERHAULED. Ориентир $5,700.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $5,700.00, max $5,700.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-04-14.</t>
         </is>
       </c>
     </row>
@@ -22376,9 +22384,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr">
@@ -22425,9 +22433,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I77" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J77" s="13" t="inlineStr">
@@ -22933,9 +22941,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I87" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J87" s="13" t="inlineStr">
@@ -22982,9 +22990,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I88" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J88" s="7" t="inlineStr">
@@ -23286,9 +23294,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I94" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I94" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J94" s="7" t="inlineStr">
@@ -23437,9 +23445,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I97" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J97" s="13" t="inlineStr">
@@ -23690,9 +23698,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I102" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J102" s="7" t="inlineStr">
@@ -23841,9 +23849,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J105" s="13" t="inlineStr">
@@ -23992,9 +24000,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I108" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J108" s="7" t="inlineStr">
@@ -24092,9 +24100,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I110" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J110" s="7" t="inlineStr">
@@ -24243,9 +24251,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I113" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I113" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J113" s="13" t="inlineStr">
@@ -24343,9 +24351,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I115" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J115" s="13" t="inlineStr">
@@ -24392,9 +24400,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I116" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J116" s="7" t="inlineStr">
@@ -24492,9 +24500,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I118" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J118" s="7" t="inlineStr">
@@ -24745,9 +24753,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I123" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J123" s="13" t="inlineStr">
@@ -25202,9 +25210,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I132" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J132" s="7" t="inlineStr">
@@ -25863,9 +25871,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I145" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J145" s="13" t="inlineStr">
@@ -25963,9 +25971,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I147" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J147" s="13" t="inlineStr">
@@ -26063,9 +26071,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I149" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J149" s="13" t="inlineStr">
@@ -26214,9 +26222,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I152" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J152" s="7" t="inlineStr">
@@ -26263,9 +26271,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I153" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J153" s="13" t="inlineStr">
@@ -26414,9 +26422,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I156" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J156" s="7" t="inlineStr">
@@ -26718,9 +26726,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I162" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J162" s="7" t="inlineStr">
@@ -26767,9 +26775,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I163" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J163" s="13" t="inlineStr">
@@ -26816,9 +26824,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I164" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I164" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J164" s="7" t="inlineStr">
@@ -26865,9 +26873,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I165" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I165" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J165" s="13" t="inlineStr">
@@ -27067,9 +27075,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I169" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I169" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J169" s="13" t="inlineStr">
@@ -27167,9 +27175,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I171" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J171" s="13" t="inlineStr">
@@ -27522,9 +27530,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I178" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I178" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J178" s="7" t="inlineStr">
@@ -27571,9 +27579,9 @@
           <t>н/п</t>
         </is>
       </c>
-      <c r="I179" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I179" s="16" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="J179" s="13" t="inlineStr">
@@ -59939,10 +59947,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -60083,31 +60091,43 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>заказов нет, но есть запросы/предложения ТУЗ/EXP</t>
+          <t>заказов нет, но в ТУЗ/EXP есть Offered/Sell Price</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>нет данных</t>
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>есть запросы, но нет предложений</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>запросы ТУЗ/EXP есть, но Offered/Sell ни разу не заполняли</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>нет данных</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>нет заказов и запросов по P/N</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Ликвидность и балл скрыты: сортировка по ним сохранена в ранге. Детали — в обосновании.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
+        <is>
+          <t>Ликвидность и балл скрыты: сортировка по ним сохранена в ранге. Детали — в обосновании.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>В ориентир НЕ входят: Закупка, Supplier/Root Price, Market Price EA.</t>
         </is>

--- a/output/ATI_liquidity_assessment.xlsx
+++ b/output/ATI_liquidity_assessment.xlsx
@@ -607,7 +607,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата отчёта: 2026-07-28 16:38 | Источники: ТАЗ (несколько периодов), ТУЗ, EXPENDABLES/CSV, АТИ</t>
+          <t>Дата отчёта: 2026-07-29 07:37 | Источники: ТАЗ (несколько периодов), ТУЗ, EXPENDABLES/CSV, АТИ</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>80908</v>
+        <v>80910</v>
       </c>
     </row>
     <row r="26">
@@ -1002,7 +1002,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>• Offered в ТУЗ иногда содержит два числа в одной ячейке (две строки) — сейчас берём верхнее число.</t>
+          <t>• Offered в ТУЗ иногда содержит два числа в одной ячейке (две строки) — сейчас берём нижнее число (минимум).</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>• ТУЗ TUZ_17.07.2026.xlsx: 37692 строк запросов</t>
+          <t>• ТУЗ TUZ_17.07.2026.xlsx: 37693 строк запросов</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>• ТУЗ ТУЗ 6_19.xlsx: 51970 строк запросов</t>
+          <t>• ТУЗ ТУЗ 6_19.xlsx: 51972 строк запросов</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 17 · клиенты: S7 Engineering, Смартавиа, Nordwind, Utair (8 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 17 · клиенты: Смартавиа, Nordwind, Utair, СмартАвиа (8 уник.)</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 8 — S7 Engineering, Смартавиа, Nordwind, Utair, СмартАвиа, qty≈42.4118). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (17 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 8 — Смартавиа, Nordwind, Utair, СмартАвиа, Якутия, qty≈44). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (17 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -2835,12 +2835,12 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: МБК-С, Руслайн, ЮВТ, Тулпар Техник (5 уник.) | Запросы ТУЗ+EXP: 15 · клиенты: АК Тулпар (Джет Экспресс), Северсталь, Тулпар Эйр, ЮВТ (8 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Тулпар, МБК-С (5 уник.) | Запросы ТУЗ+EXP: 15 · клиенты: Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар (8 уник.)</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — МБК-С, Руслайн, ЮВТ, Тулпар Техник, Тулпар, qty≈476); запросов ТУЗ+EXP: 15 (уник. P/N+клиент+день; клиентов: 8 — АК Тулпар (Джет Экспресс), Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар, qty≈457). Сопоставление: ALT P/N, точное P/N. На складе: 11 шт. (2 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $7.65: медиана продажных цен ТАЗ (все даты) (n=6, min $5.00, max $18.00, последний заказ 2025-07-15). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (371 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Тулпар, МБК-С, Руслайн, qty≈476); запросов ТУЗ+EXP: 15 (уник. P/N+клиент+день; клиентов: 8 — Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар, Аллюр Сервис, qty≈457). Сопоставление: ALT P/N, точное P/N. На складе: 11 шт. (2 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $7.65: медиана продажных цен ТАЗ (все даты) (n=6, min $5.00, max $18.00, последний заказ 2025-07-15). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (371 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 4 · клиенты: Северсталь, Руслайн (2 уник.) | Запросы ТУЗ+EXP: 3 · клиенты: АК Тулпар (Джет Экспресс), Руслайн, Аллюр Сервис (3 уник.)</t>
+          <t>Заказы ТАЗ: 4 · клиенты: Северсталь, Руслайн (2 уник.) | Запросы ТУЗ+EXP: 3 · клиенты: Руслайн, АК Тулпар (Джет Экспресс), Аллюр Сервис (3 уник.)</t>
         </is>
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — Северсталь, Руслайн, qty≈58); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — АК Тулпар (Джет Экспресс), Руслайн, Аллюр Сервис, qty≈121). Сопоставление: ALT P/N, точное P/N. На складе: 249 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $169.50: медиана продажных цен ТАЗ (все даты) (n=4, min $10.00, max $175.00, последний заказ 2025-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (356 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — Северсталь, Руслайн, qty≈58); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Руслайн, АК Тулпар (Джет Экспресс), Аллюр Сервис, qty≈82.6667). Сопоставление: ALT P/N, точное P/N. На складе: 249 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $169.50: медиана продажных цен ТАЗ (все даты) (n=4, min $10.00, max $175.00, последний заказ 2025-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (356 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="K61" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 7 · клиенты: Белавиа, Аэрофлот, S7 Engineering, АК Сибирь (5 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 7 · клиенты: Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии (5 уник.)</t>
         </is>
       </c>
       <c r="L61" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 7 (уник. P/N+клиент+день; клиентов: 5 — Белавиа, Аэрофлот, S7 Engineering, АК Сибирь, Уральские Авиалинии, qty≈11.25). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 7 (уник. P/N+клиент+день; клиентов: 5 — Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии, Аэрофлот, qty≈11.5). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Руслайн, Русджет (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: Уральские Авиалинии, ЮВТ, Тулпар Техник, АК Тулпар (13 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Руслайн, Русджет (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: Уральские Авиалинии, ЮВТ, Тулпар Техник, Аллюр Сервис (13 уник.)</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Руслайн, Русджет, Дримджет, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — Уральские Авиалинии, ЮВТ, Тулпар Техник, АК Тулпар, Северо-Запад, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Руслайн, Русджет, Дримджет, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — Уральские Авиалинии, ЮВТ, Тулпар Техник, Аллюр Сервис, Северо-Запад, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -4708,12 +4708,12 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: МБК-С, Руслайн, ЮВТ, Тулпар Техник (5 уник.) | Запросы ТУЗ+EXP: 15 · клиенты: АК Тулпар (Джет Экспресс), Северсталь, Тулпар Эйр, ЮВТ (8 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Тулпар, МБК-С (5 уник.) | Запросы ТУЗ+EXP: 15 · клиенты: Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар (8 уник.)</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — МБК-С, Руслайн, ЮВТ, Тулпар Техник, Тулпар, qty≈476); запросов ТУЗ+EXP: 15 (уник. P/N+клиент+день; клиентов: 8 — АК Тулпар (Джет Экспресс), Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар, qty≈457). Сопоставление: ALT P/N, точное P/N. На складе: 11 шт. (2 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $7.65: медиана продажных цен ТАЗ (все даты) (n=6, min $5.00, max $18.00, последний заказ 2025-07-15). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (371 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Тулпар, МБК-С, Руслайн, qty≈476); запросов ТУЗ+EXP: 15 (уник. P/N+клиент+день; клиентов: 8 — Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар, Аллюр Сервис, qty≈457). Сопоставление: ALT P/N, точное P/N. На складе: 11 шт. (2 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $7.65: медиана продажных цен ТАЗ (все даты) (n=6, min $5.00, max $18.00, последний заказ 2025-07-15). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (371 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -4762,12 +4762,12 @@
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 6 · клиенты: Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс) (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн (7 уник.)</t>
+          <t>Заказы ТАЗ: 6 · клиенты: АК Тулпар (Джет Экспресс), ЛТ Сервис, Глобал Скай, Тулпар Эйр (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Ираэро, Ямал, Nordwind, Глобал Скай (7 уник.)</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс), ЛТ Сервис, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн, Тулпар Эйр, qty≈26.6667). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — АК Тулпар (Джет Экспресс), ЛТ Сервис, Глобал Скай, Тулпар Эйр, Руслайн, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Ираэро, Ямал, Nordwind, Глобал Скай, Тулпар Эйр, qty≈26.25). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5032,12 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: ЮВТ, Руслайн, Ямал (3 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: Руслайн, ЮВТ, Ямал (3 уник.)</t>
         </is>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 2 — Руслайн, Дримджет, qty≈27); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, Руслайн, Ямал, qty≈26.3333). Сопоставление: ALT P/N, ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $340.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $300.00, max $380.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-07).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 2 — Руслайн, Дримджет, qty≈27); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Руслайн, ЮВТ, Ямал, qty≈27). Сопоставление: ALT P/N, ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $340.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $300.00, max $380.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-07).</t>
         </is>
       </c>
     </row>
@@ -5302,12 +5302,12 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 17 · клиенты: S7 Engineering, Смартавиа, Nordwind, Utair (8 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 17 · клиенты: Смартавиа, Nordwind, Utair, СмартАвиа (8 уник.)</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 8 — S7 Engineering, Смартавиа, Nordwind, Utair, СмартАвиа, qty≈42.4118). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (17 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 8 — Смартавиа, Nordwind, Utair, СмартАвиа, Якутия, qty≈44). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (17 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -5626,12 +5626,12 @@
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 4 · клиенты: Северсталь, Руслайн (2 уник.) | Запросы ТУЗ+EXP: 3 · клиенты: АК Тулпар (Джет Экспресс), Руслайн, Аллюр Сервис (3 уник.)</t>
+          <t>Заказы ТАЗ: 4 · клиенты: Северсталь, Руслайн (2 уник.) | Запросы ТУЗ+EXP: 3 · клиенты: Руслайн, АК Тулпар (Джет Экспресс), Аллюр Сервис (3 уник.)</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — Северсталь, Руслайн, qty≈58); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — АК Тулпар (Джет Экспресс), Руслайн, Аллюр Сервис, qty≈121). Сопоставление: ALT P/N, точное P/N. На складе: 249 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $169.50: медиана продажных цен ТАЗ (все даты) (n=4, min $10.00, max $175.00, последний заказ 2025-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (356 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — Северсталь, Руслайн, qty≈58); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Руслайн, АК Тулпар (Джет Экспресс), Аллюр Сервис, qty≈82.6667). Сопоставление: ALT P/N, точное P/N. На складе: 249 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $169.50: медиана продажных цен ТАЗ (все даты) (n=4, min $10.00, max $175.00, последний заказ 2025-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (356 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 7 · клиенты: Белавиа, Аэрофлот, S7 Engineering, АК Сибирь (5 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 7 · клиенты: Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии (5 уник.)</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 7 (уник. P/N+клиент+день; клиентов: 5 — Белавиа, Аэрофлот, S7 Engineering, АК Сибирь, Уральские Авиалинии, qty≈11.25). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 7 (уник. P/N+клиент+день; клиентов: 5 — Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии, Аэрофлот, qty≈11.5). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
         </is>
       </c>
     </row>
@@ -6382,12 +6382,12 @@
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Авиасервис, Дримджет, АК Тулпар (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: АК Тулпар, Авиасервис, ЮВТ, Дримджет (4 уник.)</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Авиасервис, Дримджет, АК Тулпар, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — АК Тулпар, Авиасервис, ЮВТ, Дримджет, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -6652,12 +6652,12 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Ямал | Запросы ТУЗ+EXP: 4 · клиенты: Ай Флай, Ямал, СмартАвиа, Алроса (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Ямал | Запросы ТУЗ+EXP: 4 · клиенты: Алроса, Ямал, СмартАвиа, Ай Флай (4 уник.)</t>
         </is>
       </c>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Ямал, qty≈50); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Ай Флай, Ямал, СмартАвиа, Алроса, qty≈63). Сопоставление: ALT P/N, точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $101.00: медиана продажных цен ТАЗ (все даты) (n=1, min $101.00, max $101.00, последний заказ 2024-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (721 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Ямал, qty≈50); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Алроса, Ямал, СмартАвиа, Ай Флай, qty≈63). Сопоставление: ALT P/N, точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $101.00: медиана продажных цен ТАЗ (все даты) (n=1, min $101.00, max $101.00, последний заказ 2024-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (721 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -6814,12 +6814,12 @@
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 9 · клиенты: Ямал, Nordwind, Аэрофлот, Уральские Авиалинии (5 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 9 · клиенты: Nordwind, Уральские Авиалинии, Аэрофлот, Аэрофлот Техникс (5 уник.)</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 9 (уник. P/N+клиент+день; клиентов: 5 — Ямал, Nordwind, Аэрофлот, Уральские Авиалинии, Аэрофлот Техникс, qty≈143.714). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $134.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $130.00, max $160.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 9 (уник. P/N+клиент+день; клиентов: 5 — Nordwind, Уральские Авиалинии, Аэрофлот, Аэрофлот Техникс, Ямал, qty≈151.6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $134.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $130.00, max $160.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -9011,12 +9011,12 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: МБК-С, Руслайн, ЮВТ, Тулпар Техник (5 уник.) | Запросы ТУЗ+EXP: 15 · клиенты: АК Тулпар (Джет Экспресс), Северсталь, Тулпар Эйр, ЮВТ (8 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Тулпар, МБК-С (5 уник.) | Запросы ТУЗ+EXP: 15 · клиенты: Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар (8 уник.)</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — МБК-С, Руслайн, ЮВТ, Тулпар Техник, Тулпар, qty≈476); запросов ТУЗ+EXP: 15 (уник. P/N+клиент+день; клиентов: 8 — АК Тулпар (Джет Экспресс), Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар, qty≈457). Сопоставление: ALT P/N, точное P/N. На складе: 11 шт. (2 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $7.65: медиана продажных цен ТАЗ (все даты) (n=6, min $5.00, max $18.00, последний заказ 2025-07-15). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (371 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Тулпар, МБК-С, Руслайн, qty≈476); запросов ТУЗ+EXP: 15 (уник. P/N+клиент+день; клиентов: 8 — Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар, Аллюр Сервис, qty≈457). Сопоставление: ALT P/N, точное P/N. На складе: 11 шт. (2 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $7.65: медиана продажных цен ТАЗ (все даты) (n=6, min $5.00, max $18.00, последний заказ 2025-07-15). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (371 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -9173,12 +9173,12 @@
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 17 · клиенты: S7 Engineering, Смартавиа, Nordwind, Utair (8 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 17 · клиенты: Смартавиа, Nordwind, Utair, СмартАвиа (8 уник.)</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 8 — S7 Engineering, Смартавиа, Nordwind, Utair, СмартАвиа, qty≈42.4118). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (17 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 8 — Смартавиа, Nordwind, Utair, СмартАвиа, Якутия, qty≈44). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (17 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -10307,12 +10307,12 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Ираэро, ЮВТ, Скай Партнер (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: ЮВТ, Ираэро, Скай Партнер (3 уник.)</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — Ираэро, ЮВТ, Скай Партнер, qty≈9). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $670.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=3, min $640.00, max $1,950.00, последнее предложение 2025-10-03). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 291 дн. назад).</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, Ираэро, Скай Партнер, qty≈9). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $670.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=3, min $640.00, max $1,950.00, последнее предложение 2025-10-03). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 291 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -20458,12 +20458,12 @@
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: Ираэро, Руслайн (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: Руслайн, Ираэро (2 уник.)</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — Ираэро, Руслайн, qty≈6). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,100.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $10,500.00, max $19,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-09.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — Руслайн, Ираэро, qty≈6). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,100.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $10,500.00, max $19,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-09.</t>
         </is>
       </c>
     </row>
@@ -22793,12 +22793,12 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Руслайн, Русджет (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: Уральские Авиалинии, ЮВТ, Тулпар Техник, АК Тулпар (13 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Руслайн, Русджет (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: Уральские Авиалинии, ЮВТ, Тулпар Техник, Аллюр Сервис (13 уник.)</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Руслайн, Русджет, Дримджет, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — Уральские Авиалинии, ЮВТ, Тулпар Техник, АК Тулпар, Северо-Запад, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Руслайн, Русджет, Дримджет, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — Уральские Авиалинии, ЮВТ, Тулпар Техник, Аллюр Сервис, Северо-Запад, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -22901,12 +22901,12 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 6 · клиенты: Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс) (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн (7 уник.)</t>
+          <t>Заказы ТАЗ: 6 · клиенты: АК Тулпар (Джет Экспресс), ЛТ Сервис, Глобал Скай, Тулпар Эйр (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Ираэро, Ямал, Nordwind, Глобал Скай (7 уник.)</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс), ЛТ Сервис, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн, Тулпар Эйр, qty≈26.6667). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — АК Тулпар (Джет Экспресс), ЛТ Сервис, Глобал Скай, Тулпар Эйр, Руслайн, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Ираэро, Ямал, Nordwind, Глобал Скай, Тулпар Эйр, qty≈26.25). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
         </is>
       </c>
     </row>
@@ -23063,12 +23063,12 @@
       </c>
       <c r="K7" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: ЮВТ, Руслайн, Ямал (3 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: Руслайн, ЮВТ, Ямал (3 уник.)</t>
         </is>
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 2 — Руслайн, Дримджет, qty≈27); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, Руслайн, Ямал, qty≈26.3333). Сопоставление: ALT P/N, ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $340.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $300.00, max $380.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-07).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 2 — Руслайн, Дримджет, qty≈27); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Руслайн, ЮВТ, Ямал, qty≈27). Сопоставление: ALT P/N, ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $340.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $300.00, max $380.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-07).</t>
         </is>
       </c>
     </row>
@@ -23495,12 +23495,12 @@
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 4 · клиенты: Северсталь, Руслайн (2 уник.) | Запросы ТУЗ+EXP: 3 · клиенты: АК Тулпар (Джет Экспресс), Руслайн, Аллюр Сервис (3 уник.)</t>
+          <t>Заказы ТАЗ: 4 · клиенты: Северсталь, Руслайн (2 уник.) | Запросы ТУЗ+EXP: 3 · клиенты: Руслайн, АК Тулпар (Джет Экспресс), Аллюр Сервис (3 уник.)</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — Северсталь, Руслайн, qty≈58); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — АК Тулпар (Джет Экспресс), Руслайн, Аллюр Сервис, qty≈121). Сопоставление: ALT P/N, точное P/N. На складе: 249 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $169.50: медиана продажных цен ТАЗ (все даты) (n=4, min $10.00, max $175.00, последний заказ 2025-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (356 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — Северсталь, Руслайн, qty≈58); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Руслайн, АК Тулпар (Джет Экспресс), Аллюр Сервис, qty≈82.6667). Сопоставление: ALT P/N, точное P/N. На складе: 249 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $169.50: медиана продажных цен ТАЗ (все даты) (n=4, min $10.00, max $175.00, последний заказ 2025-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (356 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -23981,12 +23981,12 @@
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 7 · клиенты: Белавиа, Аэрофлот, S7 Engineering, АК Сибирь (5 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 7 · клиенты: Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии (5 уник.)</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 7 (уник. P/N+клиент+день; клиентов: 5 — Белавиа, Аэрофлот, S7 Engineering, АК Сибирь, Уральские Авиалинии, qty≈11.25). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 7 (уник. P/N+клиент+день; клиентов: 5 — Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии, Аэрофлот, qty≈11.5). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
         </is>
       </c>
     </row>
@@ -24143,12 +24143,12 @@
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Авиасервис, Дримджет, АК Тулпар (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: АК Тулпар, Авиасервис, ЮВТ, Дримджет (4 уник.)</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Авиасервис, Дримджет, АК Тулпар, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — АК Тулпар, Авиасервис, ЮВТ, Дримджет, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -24305,12 +24305,12 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Ямал | Запросы ТУЗ+EXP: 4 · клиенты: Ай Флай, Ямал, СмартАвиа, Алроса (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Ямал | Запросы ТУЗ+EXP: 4 · клиенты: Алроса, Ямал, СмартАвиа, Ай Флай (4 уник.)</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Ямал, qty≈50); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Ай Флай, Ямал, СмартАвиа, Алроса, qty≈63). Сопоставление: ALT P/N, точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $101.00: медиана продажных цен ТАЗ (все даты) (n=1, min $101.00, max $101.00, последний заказ 2024-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (721 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Ямал, qty≈50); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Алроса, Ямал, СмартАвиа, Ай Флай, qty≈63). Сопоставление: ALT P/N, точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $101.00: медиана продажных цен ТАЗ (все даты) (n=1, min $101.00, max $101.00, последний заказ 2024-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (721 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -24467,12 +24467,12 @@
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 9 · клиенты: Ямал, Nordwind, Аэрофлот, Уральские Авиалинии (5 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 9 · клиенты: Nordwind, Уральские Авиалинии, Аэрофлот, Аэрофлот Техникс (5 уник.)</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 9 (уник. P/N+клиент+день; клиентов: 5 — Ямал, Nordwind, Аэрофлот, Уральские Авиалинии, Аэрофлот Техникс, qty≈143.714). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $134.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $130.00, max $160.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 9 (уник. P/N+клиент+день; клиентов: 5 — Nordwind, Уральские Авиалинии, Аэрофлот, Аэрофлот Техникс, Ямал, qty≈151.6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $134.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $130.00, max $160.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -26465,12 +26465,12 @@
       </c>
       <c r="K70" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Аэрофлот Техникс, Nordwind (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Nordwind, Аэрофлот Техникс (3 уник.)</t>
         </is>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Аэрофлот, Аэрофлот Техникс, Nordwind, qty≈142). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $213.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=6, min $127.00, max $310.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Аэрофлот, Nordwind, Аэрофлот Техникс, qty≈115.25). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $213.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=6, min $127.00, max $310.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -26789,12 +26789,12 @@
       </c>
       <c r="K76" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: Северо-Запад, Аэрофлот Техникс, Аэрофлот (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: Аэрофлот, Северо-Запад, Аэрофлот Техникс (3 уник.)</t>
         </is>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Северо-Запад, Аэрофлот Техникс, Аэрофлот, qty≈66). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $203.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=3, min $190.00, max $216.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Аэрофлот, Северо-Запад, Аэрофлот Техникс, qty≈66). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $203.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=3, min $190.00, max $216.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -27059,12 +27059,12 @@
       </c>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Аэрофлот | Запросы ТУЗ+EXP: 2 · клиенты: Уральские Авиалинии, Аэрофлот (2 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Аэрофлот | Запросы ТУЗ+EXP: 2 · клиенты: Аэрофлот, Уральские Авиалинии (2 уник.)</t>
         </is>
       </c>
       <c r="L81" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Аэрофлот, qty≈2); запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Уральские Авиалинии, Аэрофлот, qty≈7). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,560.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,560.00, max $2,560.00, последний заказ 2024-09-18). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (671 дн. назад).</t>
+          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Аэрофлот, qty≈2); запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Аэрофлот, Уральские Авиалинии, qty≈7). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,560.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,560.00, max $2,560.00, последний заказ 2024-09-18). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (671 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -27491,12 +27491,12 @@
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Ираэро, ЮВТ, Скай Партнер (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: ЮВТ, Ираэро, Скай Партнер (3 уник.)</t>
         </is>
       </c>
       <c r="L89" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — Ираэро, ЮВТ, Скай Партнер, qty≈9). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $670.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=3, min $640.00, max $1,950.00, последнее предложение 2025-10-03). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 291 дн. назад).</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, Ираэро, Скай Партнер, qty≈9). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $670.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=3, min $640.00, max $1,950.00, последнее предложение 2025-10-03). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 291 дн. назад).</t>
         </is>
       </c>
     </row>

--- a/output/ATI_liquidity_assessment.xlsx
+++ b/output/ATI_liquidity_assessment.xlsx
@@ -96,17 +96,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C47F00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="002F6FED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F7F9FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C47F00"/>
       </patternFill>
     </fill>
     <fill>
@@ -200,28 +200,28 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -246,12 +246,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата отчёта: 2026-07-30 12:45 | Источники: ТАЗ (несколько периодов), ТУЗ, EXPENDABLES/CSV, АТИ</t>
+          <t>Дата отчёта: 2026-07-30 13:21 | Источники: ТАЗ (несколько периодов), ТУЗ, EXPENDABLES/CSV, АТИ</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>4003839.01</v>
+        <v>3895039.01</v>
       </c>
     </row>
     <row r="24">
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>80910</v>
+        <v>82107</v>
       </c>
     </row>
     <row r="26">
@@ -1072,7 +1072,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>• ТУЗ TUZ_17.07.2026.xlsx: 37693 строк запросов</t>
+          <t>• ТУЗ TUZ_17.07.2026.xlsx: 39025 строк запросов</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>• ТУЗ ТУЗ 6_19.xlsx: 51972 строк запросов</t>
+          <t>• ТУЗ ТУЗ 6_19.xlsx: 53288 строк запросов</t>
         </is>
       </c>
     </row>
@@ -1280,14 +1280,14 @@
         <v>32</v>
       </c>
       <c r="G2" s="10" t="n">
-        <v>11350</v>
+        <v>7950</v>
       </c>
       <c r="H2" s="10" t="n">
-        <v>363200</v>
+        <v>254400</v>
       </c>
       <c r="I2" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J2" s="12" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Белавиа, Аэрофлот (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Белавиа, S7, Аэрофлот (3 уник.)</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 2 — Белавиа, Аэрофлот, qty≈7). Сопоставление: точное P/N. На складе: 32 шт. (4 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $11,350.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=2, min $9,700.00, max $13,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-05-20.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Белавиа, S7, Аэрофлот, qty≈8). Сопоставление: точное P/N. На складе: 32 шт. (4 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $7,950.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=4, min $4,000.00, max $13,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-07.</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       <c r="H3" s="16" t="n">
         <v>184500</v>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1393,7 +1393,7 @@
       <c r="H4" s="10" t="n">
         <v>176000</v>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1447,7 +1447,7 @@
       <c r="H5" s="16" t="n">
         <v>154500</v>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1501,7 +1501,7 @@
       <c r="H6" s="10" t="n">
         <v>124200</v>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1555,7 +1555,7 @@
       <c r="H7" s="16" t="n">
         <v>101400</v>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1609,7 +1609,7 @@
       <c r="H8" s="10" t="n">
         <v>101400</v>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1663,7 +1663,7 @@
       <c r="H9" s="16" t="n">
         <v>100000</v>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I9" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -1717,7 +1717,7 @@
       <c r="H10" s="10" t="n">
         <v>92400</v>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1771,7 +1771,7 @@
       <c r="H11" s="16" t="n">
         <v>86800</v>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1825,7 +1825,7 @@
       <c r="H12" s="10" t="n">
         <v>86294.39999999999</v>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -1879,7 +1879,7 @@
       <c r="H13" s="16" t="n">
         <v>75000</v>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1933,7 +1933,7 @@
       <c r="H14" s="10" t="n">
         <v>74400</v>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: ЛТ Сервис | Запросы ТУЗ+EXP: 3 · клиенты: ЮВТ, АК Тулпар, Ямал (3 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: ЛТ Сервис | Запросы ТУЗ+EXP: 3 · клиенты: Ямал, ЮВТ, АК Тулпар (3 уник.)</t>
         </is>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — ЛТ Сервис, qty≈1); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, АК Тулпар, Ямал, qty≈3). Сопоставление: ALT P/N, точное P/N. На складе: 6 шт. (6 строк АТИ). Состояние склада: REPAIRED / BER?; SERVICEABLE. Ориентир $12,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $12,400.00, max $12,400.00, последний заказ 2023-01-20). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1278 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — ЛТ Сервис, qty≈1); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Ямал, ЮВТ, АК Тулпар, qty≈3). Сопоставление: ALT P/N, точное P/N. На складе: 6 шт. (6 строк АТИ). Состояние склада: REPAIRED / BER?; SERVICEABLE. Ориентир $12,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $12,400.00, max $12,400.00, последний заказ 2023-01-20). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1278 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       <c r="H15" s="16" t="n">
         <v>70000</v>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2041,7 +2041,7 @@
       <c r="H16" s="10" t="n">
         <v>67900</v>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2095,7 +2095,7 @@
       <c r="H17" s="16" t="n">
         <v>61950</v>
       </c>
-      <c r="I17" s="18" t="inlineStr">
+      <c r="I17" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2149,7 +2149,7 @@
       <c r="H18" s="10" t="n">
         <v>60800</v>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2161,12 +2161,12 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Тулпар Эйр | Запросы ТУЗ+EXP: 6 · клиенты: Скай Партнер, Ираэро, Ямал, Тулпар Эйр (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Тулпар Эйр | Запросы ТУЗ+EXP: 6 · клиенты: Ираэро, Ямал, Тулпар Эйр, Дримджет (5 уник.)</t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Тулпар Эйр, qty≈1); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — Скай Партнер, Ираэро, Ямал, Тулпар Эйр, Дримджет, qty≈6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 4 шт. (4 строк АТИ). Состояние склада: OVERHAULED; SERVICEABLE. Ориентир $15,200.00: медиана продажных цен ТАЗ (все даты) (n=1, min $15,200.00, max $15,200.00, последний заказ 2025-04-11). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (466 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Тулпар Эйр, qty≈1); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — Ираэро, Ямал, Тулпар Эйр, Дримджет, Скай Партнер, qty≈6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 4 шт. (4 строк АТИ). Состояние склада: OVERHAULED; SERVICEABLE. Ориентир $15,200.00: медиана продажных цен ТАЗ (все даты) (n=1, min $15,200.00, max $15,200.00, последний заказ 2025-04-11). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (466 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       <c r="H19" s="16" t="n">
         <v>56700</v>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2257,7 +2257,7 @@
       <c r="H20" s="10" t="n">
         <v>49200</v>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2311,7 +2311,7 @@
       <c r="H21" s="16" t="n">
         <v>48000</v>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2365,7 +2365,7 @@
       <c r="H22" s="10" t="n">
         <v>47750</v>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2419,7 +2419,7 @@
       <c r="H23" s="16" t="n">
         <v>47100</v>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2473,7 +2473,7 @@
       <c r="H24" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2527,7 +2527,7 @@
       <c r="H25" s="16" t="n">
         <v>44800</v>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2581,7 +2581,7 @@
       <c r="H26" s="10" t="n">
         <v>42300</v>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2635,7 +2635,7 @@
       <c r="H27" s="16" t="n">
         <v>42205.5</v>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2689,7 +2689,7 @@
       <c r="H28" s="10" t="n">
         <v>40800</v>
       </c>
-      <c r="I28" s="18" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2743,7 +2743,7 @@
       <c r="H29" s="16" t="n">
         <v>40600</v>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2797,7 +2797,7 @@
       <c r="H30" s="10" t="n">
         <v>37000</v>
       </c>
-      <c r="I30" s="11" t="inlineStr">
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -2851,7 +2851,7 @@
       <c r="H31" s="16" t="n">
         <v>35100</v>
       </c>
-      <c r="I31" s="18" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2905,7 +2905,7 @@
       <c r="H32" s="10" t="n">
         <v>543.2</v>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -2917,12 +2917,12 @@
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Руслайн, Русджет (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: Аллюр Сервис, Северо-Запад, Ямал, S7 Engineering (13 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Русджет, Дримджет, ЮВТ (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: АК Тулпар, Северо-Запад, Аллюр Сервис, Русджет (13 уник.)</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Руслайн, Русджет, Дримджет, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — Аллюр Сервис, Северо-Запад, Ямал, S7 Engineering, Азимут, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — Руслайн, Русджет, Дримджет, ЮВТ, Тулпар Техник, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — АК Тулпар, Северо-Запад, Аллюр Сервис, Русджет, Тулпар Техник, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       <c r="H33" s="16" t="n">
         <v>330</v>
       </c>
-      <c r="I33" s="17" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3013,7 +3013,7 @@
       <c r="H34" s="10" t="n">
         <v>3050</v>
       </c>
-      <c r="I34" s="17" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3025,12 +3025,12 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 6 · клиенты: АК Тулпар (Джет Экспресс), ЛТ Сервис, Глобал Скай, Тулпар Эйр (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Глобал Скай, Тулпар Эйр, Ираэро, Руслайн (7 уник.)</t>
+          <t>Заказы ТАЗ: 6 · клиенты: Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс) (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн (7 уник.)</t>
         </is>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — АК Тулпар (Джет Экспресс), ЛТ Сервис, Глобал Скай, Тулпар Эйр, Руслайн, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Глобал Скай, Тулпар Эйр, Ираэро, Руслайн, ТАРП Авиэйшн, qty≈26.25). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс), ЛТ Сервис, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн, Ямал, qty≈26.6667). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       <c r="H35" s="16" t="n">
         <v>798</v>
       </c>
-      <c r="I35" s="17" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3121,7 +3121,7 @@
       <c r="H36" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="I36" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3175,7 +3175,7 @@
       <c r="H37" s="16" t="n">
         <v>256</v>
       </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3229,7 +3229,7 @@
       <c r="H38" s="10" t="n">
         <v>13700</v>
       </c>
-      <c r="I38" s="17" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3241,12 +3241,12 @@
       </c>
       <c r="K38" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 4 · клиенты: Ираэро, Руслайн, Дримджет (3 уник.) | Запросы ТУЗ+EXP: 12 · клиенты: ЮВТ, Руслайн, АК Тулпар, Тулпар Эйр (7 уник.)</t>
+          <t>Заказы ТАЗ: 4 · клиенты: Ираэро, Руслайн, Дримджет (3 уник.) | Запросы ТУЗ+EXP: 12 · клиенты: Тулпар Эйр, Ираэро, Руслайн, Тулпар Аэро (7 уник.)</t>
         </is>
       </c>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 3 — Ираэро, Руслайн, Дримджет, qty≈4); запросов ТУЗ+EXP: 12 (уник. P/N+клиент+день; клиентов: 7 — ЮВТ, Руслайн, АК Тулпар, Тулпар Эйр, Ираэро, qty≈13). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $13,700.00: медиана продажных цен ТАЗ (все даты) (n=3, min $13,150.00, max $14,000.00, последний заказ 2025-09-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (300 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 3 — Ираэро, Руслайн, Дримджет, qty≈4); запросов ТУЗ+EXP: 12 (уник. P/N+клиент+день; клиентов: 7 — Тулпар Эйр, Ираэро, Руслайн, Тулпар Аэро, Аллюр Сервис, qty≈12.8). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $13,700.00: медиана продажных цен ТАЗ (все даты) (n=3, min $13,150.00, max $14,000.00, последний заказ 2025-09-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (300 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3283,7 @@
       <c r="H39" s="16" t="n">
         <v>340</v>
       </c>
-      <c r="I39" s="17" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3337,7 +3337,7 @@
       <c r="H40" s="10" t="n">
         <v>32800</v>
       </c>
-      <c r="I40" s="17" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3391,7 +3391,7 @@
       <c r="H41" s="16" t="n">
         <v>7600</v>
       </c>
-      <c r="I41" s="17" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3445,7 +3445,7 @@
       <c r="H42" s="10" t="n">
         <v>3800</v>
       </c>
-      <c r="I42" s="17" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3499,7 +3499,7 @@
       <c r="H43" s="16" t="n">
         <v>2610</v>
       </c>
-      <c r="I43" s="17" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3553,7 +3553,7 @@
       <c r="H44" s="10" t="n">
         <v>587.8</v>
       </c>
-      <c r="I44" s="17" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3607,7 +3607,7 @@
       <c r="H45" s="16" t="n">
         <v>1.55</v>
       </c>
-      <c r="I45" s="17" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3661,7 +3661,7 @@
       <c r="H46" s="10" t="n">
         <v>10.9</v>
       </c>
-      <c r="I46" s="17" t="inlineStr">
+      <c r="I46" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3715,7 +3715,7 @@
       <c r="H47" s="16" t="n">
         <v>17900</v>
       </c>
-      <c r="I47" s="17" t="inlineStr">
+      <c r="I47" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3769,7 +3769,7 @@
       <c r="H48" s="10" t="n">
         <v>19566.5</v>
       </c>
-      <c r="I48" s="17" t="inlineStr">
+      <c r="I48" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: Ираэро, Джет Экспресс (2 уник.) | Запросы ТУЗ+EXP: 11 · клиенты: Дримджет, Руслайн, ЮВТ, Ираэро (4 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: Ираэро, Джет Экспресс (2 уник.) | Запросы ТУЗ+EXP: 11 · клиенты: Руслайн, Дримджет, ЮВТ, Ираэро (4 уник.)</t>
         </is>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 2 — Ираэро, Джет Экспресс, qty≈2); запросов ТУЗ+EXP: 11 (уник. P/N+клиент+день; клиентов: 4 — Дримджет, Руслайн, ЮВТ, Ираэро, qty≈13). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $19,566.50: медиана продажных цен ТАЗ (все даты) (n=2, min $11,800.00, max $27,333.00, последний заказ 2025-09-19). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (305 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 2 — Ираэро, Джет Экспресс, qty≈2); запросов ТУЗ+EXP: 11 (уник. P/N+клиент+день; клиентов: 4 — Руслайн, Дримджет, ЮВТ, Ираэро, qty≈13). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $19,566.50: медиана продажных цен ТАЗ (все даты) (n=2, min $11,800.00, max $27,333.00, последний заказ 2025-09-19). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (305 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       <c r="H49" s="16" t="n">
         <v>6200</v>
       </c>
-      <c r="I49" s="17" t="inlineStr">
+      <c r="I49" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3877,7 +3877,7 @@
       <c r="H50" s="10" t="n">
         <v>1800</v>
       </c>
-      <c r="I50" s="17" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -3904,51 +3904,51 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>979998-3</t>
+          <t>38E93-6</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>VALVE, BLEED, SHUTOFF, ISOLATION</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>OH, R</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="F51" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51" s="16" t="n">
-        <v>16500</v>
+        <v>4100</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>33000</v>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
+        <v>4100</v>
+      </c>
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>средняя (заказы ТАЗ)</t>
+      <c r="J51" s="20" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K51" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: МБК-С | Запросы ТУЗ+EXP: 8 · клиенты: АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал (6 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 8 · клиенты: Белавиа, Аэрофлот, S7 Engineering, S7 (6 уник.)</t>
         </is>
       </c>
       <c r="L51" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — МБК-С, qty≈2); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 6 — АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал, Тулпар Эйр, qty≈8). Сопоставление: точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: OVERHAULED; REPAIRED / BER?. Ориентир $16,500.00: медиана продажных цен ТАЗ (все даты) (n=1, min $16,500.00, max $16,500.00, последний заказ 2023-03-02). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1237 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 6 — Белавиа, Аэрофлот, S7 Engineering, S7, АК Сибирь, qty≈12.4). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
         </is>
       </c>
     </row>
@@ -3958,51 +3958,51 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>0727540</t>
+          <t>979998-3</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>SHROUD</t>
+          <t>VALVE, BLEED, SHUTOFF, ISOLATION</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>OH, R</t>
         </is>
       </c>
       <c r="F52" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>500</v>
+        <v>16500</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>500</v>
-      </c>
-      <c r="I52" s="17" t="inlineStr">
+        <v>33000</v>
+      </c>
+      <c r="I52" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J52" s="19" t="inlineStr">
-        <is>
-          <t>низкая (предложения)</t>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K52" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: Nordwind, Уральские Авиалинии, -, Аэрофлот (7 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: МБК-С | Запросы ТУЗ+EXP: 8 · клиенты: АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал (6 уник.)</t>
         </is>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Nordwind, Уральские Авиалинии, -, Аэрофлот, АК Россия, qty≈94). Сопоставление: ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $500.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=7, min $260.00, max $5,700.00, последнее предложение 2025-01-30). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 537 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — МБК-С, qty≈2); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 6 — АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал, Тулпар Эйр, qty≈8). Сопоставление: точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: OVERHAULED; REPAIRED / BER?. Ориентир $16,500.00: медиана продажных цен ТАЗ (все даты) (n=1, min $16,500.00, max $16,500.00, последний заказ 2023-03-02). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1237 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>ABS0604-4</t>
+          <t>0727540</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>WASHER</t>
+          <t>SHROUD</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -4031,32 +4031,32 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G53" s="16" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>150</v>
-      </c>
-      <c r="I53" s="17" t="inlineStr">
+        <v>500</v>
+      </c>
+      <c r="I53" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J53" s="12" t="inlineStr">
-        <is>
-          <t>средняя (заказы ТАЗ)</t>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K53" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: VDT | Запросы ТУЗ+EXP: 8 · клиенты: Ямал, S7 Engineering, VDT, Аэрофлот Техникс (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: Nordwind, Уральские Авиалинии, -, Аэрофлот (7 уник.)</t>
         </is>
       </c>
       <c r="L53" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — VDT, qty≈170); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 4 — Ямал, S7 Engineering, VDT, Аэрофлот Техникс, qty≈1236). Сопоставление: точное P/N. На складе: 50 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3.00: медиана продажных цен ТАЗ (все даты) (n=1, min $3.00, max $3.00, последний заказ 2024-11-22). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (606 дн. назад).</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Nordwind, Уральские Авиалинии, -, Аэрофлот, АК Россия, qty≈94). Сопоставление: ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $500.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=7, min $260.00, max $5,700.00, последнее предложение 2025-01-30). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 537 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -4066,51 +4066,51 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>979998-1</t>
+          <t>ABS0604-4</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>VALVE, SHUTOFF, PRESSURE REGULATING</t>
+          <t>WASHER</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F54" s="9" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>12300</v>
+        <v>3</v>
       </c>
       <c r="H54" s="10" t="n">
-        <v>24600</v>
-      </c>
-      <c r="I54" s="17" t="inlineStr">
+        <v>150</v>
+      </c>
+      <c r="I54" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>средняя (предложения)</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 17 · клиенты: ЮВТ, Ямал, Скай Партнер, Аллюр Сервис (6 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: VDT | Запросы ТУЗ+EXP: 8 · клиенты: Ямал, S7 Engineering, VDT, Аэрофлот Техникс (4 уник.)</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 6 — ЮВТ, Ямал, Скай Партнер, Аллюр Сервис, Дримджет, qty≈18). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $12,300.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=11, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — VDT, qty≈170); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 4 — Ямал, S7 Engineering, VDT, Аэрофлот Техникс, qty≈1236). Сопоставление: точное P/N. На складе: 50 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3.00: медиана продажных цен ТАЗ (все даты) (n=1, min $3.00, max $3.00, последний заказ 2024-11-22). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (606 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -4120,51 +4120,51 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>737MAX</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>P2-07-0021-002</t>
+          <t>979998-1</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>BATTERY</t>
+          <t>VALVE, SHUTOFF, PRESSURE REGULATING</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G55" s="16" t="n">
-        <v>98</v>
+        <v>12300</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>686</v>
-      </c>
-      <c r="I55" s="17" t="inlineStr">
+        <v>24600</v>
+      </c>
+      <c r="I55" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J55" s="20" t="inlineStr">
-        <is>
-          <t>высокая (заказы ТАЗ)</t>
+      <c r="J55" s="12" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: 407 Техникс | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Белавиа, S7 Engineering, Победа (5 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 17 · клиенты: ЮВТ, Руслайн, Ямал, Скай Партнер (6 уник.)</t>
         </is>
       </c>
       <c r="L55" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — 407 Техникс, qty≈16); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — ЮВТ, Белавиа, S7 Engineering, Победа, ВТС ДЖЕТС, qty≈122). Сопоставление: точное P/N. На складе: 7 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $98.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $98.00, max $98.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-16).</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 6 — ЮВТ, Руслайн, Ямал, Скай Партнер, Аллюр Сервис, qty≈18). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $12,300.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=11, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -4174,34 +4174,34 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>737MAX</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>38E93-6</t>
+          <t>P2-07-0021-002</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>BATTERY</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F56" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>4100</v>
+        <v>98</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>4100</v>
-      </c>
-      <c r="I56" s="17" t="inlineStr">
+        <v>686</v>
+      </c>
+      <c r="I56" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4213,12 +4213,12 @@
       </c>
       <c r="K56" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 7 · клиенты: Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: 407 Техникс | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Белавиа, S7 Engineering, Победа (5 уник.)</t>
         </is>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 7 (уник. P/N+клиент+день; клиентов: 5 — Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии, Аэрофлот, qty≈11.5). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — 407 Техникс, qty≈16); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — ЮВТ, Белавиа, S7 Engineering, Победа, ВТС ДЖЕТС, qty≈122). Сопоставление: точное P/N. На складе: 7 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $98.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $98.00, max $98.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-16).</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       <c r="H57" s="16" t="n">
         <v>14300</v>
       </c>
-      <c r="I57" s="17" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4309,7 +4309,7 @@
       <c r="H58" s="10" t="n">
         <v>18900</v>
       </c>
-      <c r="I58" s="17" t="inlineStr">
+      <c r="I58" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4363,7 +4363,7 @@
       <c r="H59" s="16" t="n">
         <v>264</v>
       </c>
-      <c r="I59" s="17" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="K59" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: АК Тулпар, Авиасервис, ЮВТ, Дримджет (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Авиасервис, Дримджет, АК Тулпар (4 уник.)</t>
         </is>
       </c>
       <c r="L59" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — АК Тулпар, Авиасервис, ЮВТ, Дримджет, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Авиасервис, Дримджет, АК Тулпар, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       <c r="H60" s="10" t="n">
         <v>32000</v>
       </c>
-      <c r="I60" s="17" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4471,7 +4471,7 @@
       <c r="H61" s="16" t="n">
         <v>841.5</v>
       </c>
-      <c r="I61" s="17" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4616,7 +4616,7 @@
       <c r="H2" s="10" t="n">
         <v>543.2</v>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Руслайн, Русджет (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: Аллюр Сервис, Северо-Запад, Ямал, S7 Engineering (13 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Русджет, Дримджет, ЮВТ (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: АК Тулпар, Северо-Запад, Аллюр Сервис, Русджет (13 уник.)</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Руслайн, Русджет, Дримджет, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — Аллюр Сервис, Северо-Запад, Ямал, S7 Engineering, Азимут, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — Руслайн, Русджет, Дримджет, ЮВТ, Тулпар Техник, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — АК Тулпар, Северо-Запад, Аллюр Сервис, Русджет, Тулпар Техник, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       <c r="H3" s="16" t="n">
         <v>330</v>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4724,7 +4724,7 @@
       <c r="H4" s="10" t="n">
         <v>3050</v>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 6 · клиенты: АК Тулпар (Джет Экспресс), ЛТ Сервис, Глобал Скай, Тулпар Эйр (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Глобал Скай, Тулпар Эйр, Ираэро, Руслайн (7 уник.)</t>
+          <t>Заказы ТАЗ: 6 · клиенты: Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс) (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн (7 уник.)</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — АК Тулпар (Джет Экспресс), ЛТ Сервис, Глобал Скай, Тулпар Эйр, Руслайн, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Глобал Скай, Тулпар Эйр, Ираэро, Руслайн, ТАРП Авиэйшн, qty≈26.25). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс), ЛТ Сервис, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн, Ямал, qty≈26.6667). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4778,7 @@
       <c r="H5" s="16" t="n">
         <v>798</v>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4832,7 +4832,7 @@
       <c r="H6" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4886,7 +4886,7 @@
       <c r="H7" s="16" t="n">
         <v>256</v>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4940,7 +4940,7 @@
       <c r="H8" s="10" t="n">
         <v>13700</v>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -4952,12 +4952,12 @@
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 4 · клиенты: Ираэро, Руслайн, Дримджет (3 уник.) | Запросы ТУЗ+EXP: 12 · клиенты: ЮВТ, Руслайн, АК Тулпар, Тулпар Эйр (7 уник.)</t>
+          <t>Заказы ТАЗ: 4 · клиенты: Ираэро, Руслайн, Дримджет (3 уник.) | Запросы ТУЗ+EXP: 12 · клиенты: Тулпар Эйр, Ираэро, Руслайн, Тулпар Аэро (7 уник.)</t>
         </is>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 3 — Ираэро, Руслайн, Дримджет, qty≈4); запросов ТУЗ+EXP: 12 (уник. P/N+клиент+день; клиентов: 7 — ЮВТ, Руслайн, АК Тулпар, Тулпар Эйр, Ираэро, qty≈13). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $13,700.00: медиана продажных цен ТАЗ (все даты) (n=3, min $13,150.00, max $14,000.00, последний заказ 2025-09-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (300 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 3 — Ираэро, Руслайн, Дримджет, qty≈4); запросов ТУЗ+EXP: 12 (уник. P/N+клиент+день; клиентов: 7 — Тулпар Эйр, Ираэро, Руслайн, Тулпар Аэро, Аллюр Сервис, qty≈12.8). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $13,700.00: медиана продажных цен ТАЗ (все даты) (n=3, min $13,150.00, max $14,000.00, последний заказ 2025-09-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (300 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       <c r="H9" s="16" t="n">
         <v>340</v>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5048,7 +5048,7 @@
       <c r="H10" s="10" t="n">
         <v>82000</v>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5102,7 +5102,7 @@
       <c r="H11" s="16" t="n">
         <v>202800</v>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5156,7 +5156,7 @@
       <c r="H12" s="10" t="n">
         <v>11400</v>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5210,7 +5210,7 @@
       <c r="H13" s="16" t="n">
         <v>2610</v>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5264,7 +5264,7 @@
       <c r="H14" s="10" t="n">
         <v>587.8</v>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5318,7 +5318,7 @@
       <c r="H15" s="16" t="n">
         <v>1.55</v>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5372,7 +5372,7 @@
       <c r="H16" s="10" t="n">
         <v>10.9</v>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5426,7 +5426,7 @@
       <c r="H17" s="16" t="n">
         <v>17900</v>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5480,7 +5480,7 @@
       <c r="H18" s="10" t="n">
         <v>124200</v>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5534,7 +5534,7 @@
       <c r="H19" s="16" t="n">
         <v>42205.5</v>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5588,7 +5588,7 @@
       <c r="H20" s="10" t="n">
         <v>19566.5</v>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5600,12 +5600,12 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: Ираэро, Джет Экспресс (2 уник.) | Запросы ТУЗ+EXP: 11 · клиенты: Дримджет, Руслайн, ЮВТ, Ираэро (4 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: Ираэро, Джет Экспресс (2 уник.) | Запросы ТУЗ+EXP: 11 · клиенты: Руслайн, Дримджет, ЮВТ, Ираэро (4 уник.)</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 2 — Ираэро, Джет Экспресс, qty≈2); запросов ТУЗ+EXP: 11 (уник. P/N+клиент+день; клиентов: 4 — Дримджет, Руслайн, ЮВТ, Ираэро, qty≈13). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $19,566.50: медиана продажных цен ТАЗ (все даты) (n=2, min $11,800.00, max $27,333.00, последний заказ 2025-09-19). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (305 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 2 — Ираэро, Джет Экспресс, qty≈2); запросов ТУЗ+EXP: 11 (уник. P/N+клиент+день; клиентов: 4 — Руслайн, Дримджет, ЮВТ, Ираэро, qty≈13). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $19,566.50: медиана продажных цен ТАЗ (все даты) (n=2, min $11,800.00, max $27,333.00, последний заказ 2025-09-19). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (305 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       <c r="H21" s="16" t="n">
         <v>6200</v>
       </c>
-      <c r="I21" s="17" t="inlineStr">
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5696,7 +5696,7 @@
       <c r="H22" s="10" t="n">
         <v>1800</v>
       </c>
-      <c r="I22" s="17" t="inlineStr">
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -5723,51 +5723,51 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>979998-3</t>
+          <t>38E93-6</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>VALVE, BLEED, SHUTOFF, ISOLATION</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>OH, R</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>16500</v>
+        <v>4100</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>33000</v>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
+        <v>4100</v>
+      </c>
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>средняя (заказы ТАЗ)</t>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: МБК-С | Запросы ТУЗ+EXP: 8 · клиенты: АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал (6 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 8 · клиенты: Белавиа, Аэрофлот, S7 Engineering, S7 (6 уник.)</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — МБК-С, qty≈2); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 6 — АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал, Тулпар Эйр, qty≈8). Сопоставление: точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: OVERHAULED; REPAIRED / BER?. Ориентир $16,500.00: медиана продажных цен ТАЗ (все даты) (n=1, min $16,500.00, max $16,500.00, последний заказ 2023-03-02). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1237 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 6 — Белавиа, Аэрофлот, S7 Engineering, S7, АК Сибирь, qty≈12.4). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
         </is>
       </c>
     </row>
@@ -5777,51 +5777,51 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>0727540</t>
+          <t>979998-3</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>SHROUD</t>
+          <t>VALVE, BLEED, SHUTOFF, ISOLATION</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>OH, R</t>
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>500</v>
+        <v>16500</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>500</v>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
+        <v>33000</v>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
-        <is>
-          <t>низкая (предложения)</t>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: Nordwind, Уральские Авиалинии, -, Аэрофлот (7 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: МБК-С | Запросы ТУЗ+EXP: 8 · клиенты: АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал (6 уник.)</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Nordwind, Уральские Авиалинии, -, Аэрофлот, АК Россия, qty≈94). Сопоставление: ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $500.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=7, min $260.00, max $5,700.00, последнее предложение 2025-01-30). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 537 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — МБК-С, qty≈2); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 6 — АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал, Тулпар Эйр, qty≈8). Сопоставление: точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: OVERHAULED; REPAIRED / BER?. Ориентир $16,500.00: медиана продажных цен ТАЗ (все даты) (n=1, min $16,500.00, max $16,500.00, последний заказ 2023-03-02). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1237 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -5836,12 +5836,12 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>ABS0604-4</t>
+          <t>0727540</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>WASHER</t>
+          <t>SHROUD</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -5850,32 +5850,32 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>150</v>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
+        <v>500</v>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J25" s="12" t="inlineStr">
-        <is>
-          <t>средняя (заказы ТАЗ)</t>
+      <c r="J25" s="19" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: VDT | Запросы ТУЗ+EXP: 8 · клиенты: Ямал, S7 Engineering, VDT, Аэрофлот Техникс (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: Nordwind, Уральские Авиалинии, -, Аэрофлот (7 уник.)</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — VDT, qty≈170); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 4 — Ямал, S7 Engineering, VDT, Аэрофлот Техникс, qty≈1236). Сопоставление: точное P/N. На складе: 50 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3.00: медиана продажных цен ТАЗ (все даты) (n=1, min $3.00, max $3.00, последний заказ 2024-11-22). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (606 дн. назад).</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Nordwind, Уральские Авиалинии, -, Аэрофлот, АК Россия, qty≈94). Сопоставление: ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $500.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=7, min $260.00, max $5,700.00, последнее предложение 2025-01-30). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 537 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -5885,51 +5885,51 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>979998-1</t>
+          <t>ABS0604-4</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>VALVE, SHUTOFF, PRESSURE REGULATING</t>
+          <t>WASHER</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F26" s="9" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>12300</v>
+        <v>3</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>24600</v>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
+        <v>150</v>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>средняя (предложения)</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 17 · клиенты: ЮВТ, Ямал, Скай Партнер, Аллюр Сервис (6 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: VDT | Запросы ТУЗ+EXP: 8 · клиенты: Ямал, S7 Engineering, VDT, Аэрофлот Техникс (4 уник.)</t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 6 — ЮВТ, Ямал, Скай Партнер, Аллюр Сервис, Дримджет, qty≈18). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $12,300.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=11, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — VDT, qty≈170); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 4 — Ямал, S7 Engineering, VDT, Аэрофлот Техникс, qty≈1236). Сопоставление: точное P/N. На складе: 50 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3.00: медиана продажных цен ТАЗ (все даты) (n=1, min $3.00, max $3.00, последний заказ 2024-11-22). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (606 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -5939,51 +5939,51 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>737MAX</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>P2-07-0021-002</t>
+          <t>979998-1</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>BATTERY</t>
+          <t>VALVE, SHUTOFF, PRESSURE REGULATING</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G27" s="16" t="n">
-        <v>98</v>
+        <v>12300</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>686</v>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
+        <v>24600</v>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J27" s="20" t="inlineStr">
-        <is>
-          <t>высокая (заказы ТАЗ)</t>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: 407 Техникс | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Белавиа, S7 Engineering, Победа (5 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 17 · клиенты: ЮВТ, Руслайн, Ямал, Скай Партнер (6 уник.)</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — 407 Техникс, qty≈16); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — ЮВТ, Белавиа, S7 Engineering, Победа, ВТС ДЖЕТС, qty≈122). Сопоставление: точное P/N. На складе: 7 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $98.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $98.00, max $98.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-16).</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 6 — ЮВТ, Руслайн, Ямал, Скай Партнер, Аллюр Сервис, qty≈18). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $12,300.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=11, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -5993,34 +5993,34 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>737MAX</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>38E93-6</t>
+          <t>P2-07-0021-002</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>BATTERY</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>4100</v>
+        <v>98</v>
       </c>
       <c r="H28" s="10" t="n">
-        <v>4100</v>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
+        <v>686</v>
+      </c>
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6032,12 +6032,12 @@
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 7 · клиенты: Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: 407 Техникс | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Белавиа, S7 Engineering, Победа (5 уник.)</t>
         </is>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 7 (уник. P/N+клиент+день; клиентов: 5 — Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии, Аэрофлот, qty≈11.5). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — 407 Техникс, qty≈16); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — ЮВТ, Белавиа, S7 Engineering, Победа, ВТС ДЖЕТС, qty≈122). Сопоставление: точное P/N. На складе: 7 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $98.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $98.00, max $98.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-16).</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       <c r="H29" s="16" t="n">
         <v>14300</v>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6128,7 +6128,7 @@
       <c r="H30" s="10" t="n">
         <v>75600</v>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6182,7 +6182,7 @@
       <c r="H31" s="16" t="n">
         <v>264</v>
       </c>
-      <c r="I31" s="17" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6194,12 +6194,12 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: АК Тулпар, Авиасервис, ЮВТ, Дримджет (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Авиасервис, Дримджет, АК Тулпар (4 уник.)</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — АК Тулпар, Авиасервис, ЮВТ, Дримджет, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Авиасервис, Дримджет, АК Тулпар, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       <c r="H32" s="10" t="n">
         <v>32000</v>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6290,7 +6290,7 @@
       <c r="H33" s="16" t="n">
         <v>841.5</v>
       </c>
-      <c r="I33" s="17" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6344,7 +6344,7 @@
       <c r="H34" s="10" t="n">
         <v>44800</v>
       </c>
-      <c r="I34" s="17" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6398,7 +6398,7 @@
       <c r="H35" s="16" t="n">
         <v>505</v>
       </c>
-      <c r="I35" s="17" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6410,12 +6410,12 @@
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Ямал | Запросы ТУЗ+EXP: 4 · клиенты: Алроса, Ямал, СмартАвиа, Ай Флай (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Ямал | Запросы ТУЗ+EXP: 4 · клиенты: Ай Флай, Ямал, СмартАвиа, Алроса (4 уник.)</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Ямал, qty≈50); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Алроса, Ямал, СмартАвиа, Ай Флай, qty≈63). Сопоставление: ALT P/N, точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $101.00: медиана продажных цен ТАЗ (все даты) (n=1, min $101.00, max $101.00, последний заказ 2024-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (721 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Ямал, qty≈50); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Ай Флай, Ямал, СмартАвиа, Алроса, qty≈63). Сопоставление: ALT P/N, точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $101.00: медиана продажных цен ТАЗ (все даты) (n=1, min $101.00, max $101.00, последний заказ 2024-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (721 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       <c r="H36" s="10" t="n">
         <v>360.6</v>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="I36" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6506,7 +6506,7 @@
       <c r="H37" s="16" t="n">
         <v>76000</v>
       </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6518,12 +6518,12 @@
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Тулпар Эйр | Запросы ТУЗ+EXP: 6 · клиенты: Скай Партнер, Ираэро, Ямал, Тулпар Эйр (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Тулпар Эйр | Запросы ТУЗ+EXP: 6 · клиенты: Ираэро, Ямал, Тулпар Эйр, Дримджет (5 уник.)</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Тулпар Эйр, qty≈1); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — Скай Партнер, Ираэро, Ямал, Тулпар Эйр, Дримджет, qty≈6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 4 шт. (4 строк АТИ). Состояние склада: OVERHAULED; SERVICEABLE. Ориентир $15,200.00: медиана продажных цен ТАЗ (все даты) (n=1, min $15,200.00, max $15,200.00, последний заказ 2025-04-11). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (466 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Тулпар Эйр, qty≈1); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — Ираэро, Ямал, Тулпар Эйр, Дримджет, Скай Партнер, qty≈6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 4 шт. (4 строк АТИ). Состояние склада: OVERHAULED; SERVICEABLE. Ориентир $15,200.00: медиана продажных цен ТАЗ (все даты) (n=1, min $15,200.00, max $15,200.00, последний заказ 2025-04-11). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (466 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       <c r="H38" s="10" t="n">
         <v>402</v>
       </c>
-      <c r="I38" s="17" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6614,7 +6614,7 @@
       <c r="H39" s="16" t="n">
         <v>635</v>
       </c>
-      <c r="I39" s="17" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6668,7 +6668,7 @@
       <c r="H40" s="10" t="n">
         <v>23000</v>
       </c>
-      <c r="I40" s="17" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6722,7 +6722,7 @@
       <c r="H41" s="16" t="n">
         <v>200.48</v>
       </c>
-      <c r="I41" s="17" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6776,7 +6776,7 @@
       <c r="H42" s="10" t="n">
         <v>16600</v>
       </c>
-      <c r="I42" s="17" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6830,7 +6830,7 @@
       <c r="H43" s="16" t="n">
         <v>1850</v>
       </c>
-      <c r="I43" s="17" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6884,7 +6884,7 @@
       <c r="H44" s="10" t="n">
         <v>12120</v>
       </c>
-      <c r="I44" s="17" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6938,7 +6938,7 @@
       <c r="H45" s="16" t="n">
         <v>8000</v>
       </c>
-      <c r="I45" s="17" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -6992,7 +6992,7 @@
       <c r="H46" s="10" t="n">
         <v>2670</v>
       </c>
-      <c r="I46" s="17" t="inlineStr">
+      <c r="I46" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7046,7 +7046,7 @@
       <c r="H47" s="16" t="n">
         <v>16380</v>
       </c>
-      <c r="I47" s="17" t="inlineStr">
+      <c r="I47" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7100,7 +7100,7 @@
       <c r="H48" s="10" t="n">
         <v>16000</v>
       </c>
-      <c r="I48" s="17" t="inlineStr">
+      <c r="I48" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7154,7 +7154,7 @@
       <c r="H49" s="16" t="n">
         <v>21000</v>
       </c>
-      <c r="I49" s="17" t="inlineStr">
+      <c r="I49" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7208,7 +7208,7 @@
       <c r="H50" s="10" t="n">
         <v>9400</v>
       </c>
-      <c r="I50" s="17" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7262,7 +7262,7 @@
       <c r="H51" s="16" t="n">
         <v>9400</v>
       </c>
-      <c r="I51" s="17" t="inlineStr">
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7316,7 +7316,7 @@
       <c r="H52" s="10" t="n">
         <v>87500</v>
       </c>
-      <c r="I52" s="17" t="inlineStr">
+      <c r="I52" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7370,7 +7370,7 @@
       <c r="H53" s="16" t="n">
         <v>2800</v>
       </c>
-      <c r="I53" s="17" t="inlineStr">
+      <c r="I53" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7424,7 +7424,7 @@
       <c r="H54" s="10" t="n">
         <v>346</v>
       </c>
-      <c r="I54" s="17" t="inlineStr">
+      <c r="I54" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7478,7 +7478,7 @@
       <c r="H55" s="16" t="n">
         <v>950</v>
       </c>
-      <c r="I55" s="17" t="inlineStr">
+      <c r="I55" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7532,7 +7532,7 @@
       <c r="H56" s="10" t="n">
         <v>306</v>
       </c>
-      <c r="I56" s="17" t="inlineStr">
+      <c r="I56" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7586,7 +7586,7 @@
       <c r="H57" s="16" t="n">
         <v>176000</v>
       </c>
-      <c r="I57" s="17" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7640,7 +7640,7 @@
       <c r="H58" s="10" t="n">
         <v>139.08</v>
       </c>
-      <c r="I58" s="17" t="inlineStr">
+      <c r="I58" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7694,7 +7694,7 @@
       <c r="H59" s="16" t="n">
         <v>284</v>
       </c>
-      <c r="I59" s="17" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7748,7 +7748,7 @@
       <c r="H60" s="10" t="n">
         <v>70000</v>
       </c>
-      <c r="I60" s="17" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7802,7 +7802,7 @@
       <c r="H61" s="16" t="n">
         <v>1248</v>
       </c>
-      <c r="I61" s="17" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7814,12 +7814,12 @@
       </c>
       <c r="K61" s="14" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Nordwind, Северо-Запад, Аэрофлот, Аэрофлот Техникс (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Северо-Запад, Аэрофлот, Аэрофлот Техникс, Nordwind (4 уник.)</t>
         </is>
       </c>
       <c r="L61" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — Nordwind, Северо-Запад, Аэрофлот, Аэрофлот Техникс, qty≈129). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 6 шт. (2 строк АТИ). Состояние склада: NEW. Ориентир $208.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $120.00, max $270.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — Северо-Запад, Аэрофлот, Аэрофлот Техникс, Nordwind, qty≈129). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 6 шт. (2 строк АТИ). Состояние склада: NEW. Ориентир $208.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $120.00, max $270.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       <c r="H62" s="10" t="n">
         <v>74400</v>
       </c>
-      <c r="I62" s="17" t="inlineStr">
+      <c r="I62" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7868,12 +7868,12 @@
       </c>
       <c r="K62" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: ЛТ Сервис | Запросы ТУЗ+EXP: 3 · клиенты: ЮВТ, АК Тулпар, Ямал (3 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: ЛТ Сервис | Запросы ТУЗ+EXP: 3 · клиенты: Ямал, ЮВТ, АК Тулпар (3 уник.)</t>
         </is>
       </c>
       <c r="L62" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — ЛТ Сервис, qty≈1); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, АК Тулпар, Ямал, qty≈3). Сопоставление: ALT P/N, точное P/N. На складе: 6 шт. (6 строк АТИ). Состояние склада: REPAIRED / BER?; SERVICEABLE. Ориентир $12,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $12,400.00, max $12,400.00, последний заказ 2023-01-20). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1278 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — ЛТ Сервис, qty≈1); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Ямал, ЮВТ, АК Тулпар, qty≈3). Сопоставление: ALT P/N, точное P/N. На складе: 6 шт. (6 строк АТИ). Состояние склада: REPAIRED / BER?; SERVICEABLE. Ориентир $12,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $12,400.00, max $12,400.00, последний заказ 2023-01-20). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1278 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -7910,7 +7910,7 @@
       <c r="H63" s="16" t="n">
         <v>30400</v>
       </c>
-      <c r="I63" s="17" t="inlineStr">
+      <c r="I63" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -7964,7 +7964,7 @@
       <c r="H64" s="10" t="n">
         <v>21000</v>
       </c>
-      <c r="I64" s="17" t="inlineStr">
+      <c r="I64" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -8018,7 +8018,7 @@
       <c r="H65" s="16" t="n">
         <v>7850</v>
       </c>
-      <c r="I65" s="17" t="inlineStr">
+      <c r="I65" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -8072,7 +8072,7 @@
       <c r="H66" s="10" t="n">
         <v>9800</v>
       </c>
-      <c r="I66" s="17" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -8126,7 +8126,7 @@
       <c r="H67" s="16" t="n">
         <v>130.21</v>
       </c>
-      <c r="I67" s="17" t="inlineStr">
+      <c r="I67" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -8180,7 +8180,7 @@
       <c r="H68" s="10" t="n">
         <v>48000</v>
       </c>
-      <c r="I68" s="17" t="inlineStr">
+      <c r="I68" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -8234,7 +8234,7 @@
       <c r="H69" s="16" t="n">
         <v>955</v>
       </c>
-      <c r="I69" s="17" t="inlineStr">
+      <c r="I69" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -8288,7 +8288,7 @@
       <c r="H70" s="10" t="n">
         <v>852.5</v>
       </c>
-      <c r="I70" s="17" t="inlineStr">
+      <c r="I70" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -8342,7 +8342,7 @@
       <c r="H71" s="16" t="n">
         <v>380</v>
       </c>
-      <c r="I71" s="18" t="inlineStr">
+      <c r="I71" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8396,7 +8396,7 @@
       <c r="H72" s="10" t="n">
         <v>2660</v>
       </c>
-      <c r="I72" s="18" t="inlineStr">
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8450,7 +8450,7 @@
       <c r="H73" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="I73" s="18" t="inlineStr">
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8504,7 +8504,7 @@
       <c r="H74" s="10" t="n">
         <v>1656</v>
       </c>
-      <c r="I74" s="18" t="inlineStr">
+      <c r="I74" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8558,7 +8558,7 @@
       <c r="H75" s="16" t="n">
         <v>630.5</v>
       </c>
-      <c r="I75" s="18" t="inlineStr">
+      <c r="I75" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8570,12 +8570,12 @@
       </c>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Аэрофлот, Уральские Авиалинии, Utair, Победа (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Utair, Победа, Аэрофлот, Уральские Авиалинии (4 уник.)</t>
         </is>
       </c>
       <c r="L75" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Аэрофлот, Уральские Авиалинии, Utair, Победа, qty≈69). Сопоставление: ALT P/N, точное P/N. На складе: 13 шт. (2 строк АТИ). Состояние склада: NEW. Ориентир $48.50: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $48.00, max $49.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Utair, Победа, Аэрофлот, Уральские Авиалинии, qty≈69). Сопоставление: ALT P/N, точное P/N. На складе: 13 шт. (2 строк АТИ). Состояние склада: NEW. Ориентир $48.50: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $48.00, max $49.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       <c r="H76" s="10" t="n">
         <v>308</v>
       </c>
-      <c r="I76" s="18" t="inlineStr">
+      <c r="I76" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8666,7 +8666,7 @@
       <c r="H77" s="16" t="n">
         <v>384</v>
       </c>
-      <c r="I77" s="18" t="inlineStr">
+      <c r="I77" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8720,7 +8720,7 @@
       <c r="H78" s="10" t="n">
         <v>426</v>
       </c>
-      <c r="I78" s="18" t="inlineStr">
+      <c r="I78" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8732,12 +8732,12 @@
       </c>
       <c r="K78" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Nordwind, Аэрофлот Техникс (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Аэрофлот Техникс, Nordwind (3 уник.)</t>
         </is>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Аэрофлот, Nordwind, Аэрофлот Техникс, qty≈115.25). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $213.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=6, min $127.00, max $310.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Аэрофлот, Аэрофлот Техникс, Nordwind, qty≈142). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $213.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=6, min $127.00, max $310.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       <c r="H79" s="16" t="n">
         <v>2400</v>
       </c>
-      <c r="I79" s="18" t="inlineStr">
+      <c r="I79" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8786,12 +8786,12 @@
       </c>
       <c r="K79" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Азур Эйр | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Азур Эйр (2 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Азур Эйр | Запросы ТУЗ+EXP: 5 · клиенты: Азур Эйр, Аэрофлот (2 уник.)</t>
         </is>
       </c>
       <c r="L79" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Азур Эйр, qty≈2); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 2 — Аэрофлот, Азур Эйр, qty≈7). Сопоставление: ведущие нули, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,400.00, max $2,400.00, последний заказ 2024-01-12). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (921 дн. назад).</t>
+          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Азур Эйр, qty≈2); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 2 — Азур Эйр, Аэрофлот, qty≈7). Сопоставление: ведущие нули, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,400.00, max $2,400.00, последний заказ 2024-01-12). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (921 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8828,7 @@
       <c r="H80" s="10" t="n">
         <v>4020</v>
       </c>
-      <c r="I80" s="18" t="inlineStr">
+      <c r="I80" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -8882,7 +8882,7 @@
       <c r="H81" s="16" t="n">
         <v>1620</v>
       </c>
-      <c r="I81" s="18" t="inlineStr">
+      <c r="I81" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -9027,7 +9027,7 @@
       <c r="H2" s="10" t="n">
         <v>84.15000000000001</v>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9039,12 +9039,12 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Тулпар, МБК-С (5 уник.) | Запросы ТУЗ+EXP: 15 · клиенты: Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар (8 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: МБК-С, Руслайн, ЮВТ, Тулпар Техник (5 уник.) | Запросы ТУЗ+EXP: 15 · клиенты: АК Тулпар (Джет Экспресс), Северсталь, Тулпар Эйр, ЮВТ (8 уник.)</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Тулпар, МБК-С, Руслайн, qty≈476); запросов ТУЗ+EXP: 15 (уник. P/N+клиент+день; клиентов: 8 — Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар, Аллюр Сервис, qty≈457). Сопоставление: ALT P/N, точное P/N. На складе: 11 шт. (2 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $7.65: медиана продажных цен ТАЗ (все даты) (n=6, min $5.00, max $18.00, последний заказ 2025-07-15). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (371 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — МБК-С, Руслайн, ЮВТ, Тулпар Техник, Тулпар, qty≈476); запросов ТУЗ+EXP: 15 (уник. P/N+клиент+день; клиентов: 8 — АК Тулпар (Джет Экспресс), Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар, qty≈457). Сопоставление: ALT P/N, точное P/N. На складе: 11 шт. (2 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $7.65: медиана продажных цен ТАЗ (все даты) (n=6, min $5.00, max $18.00, последний заказ 2025-07-15). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (371 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -9081,7 +9081,7 @@
       <c r="H3" s="16" t="n">
         <v>104.5</v>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9135,7 +9135,7 @@
       <c r="H4" s="10" t="n">
         <v>720</v>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9189,7 +9189,7 @@
       <c r="H5" s="16" t="n">
         <v>29240</v>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="K5" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 17 · клиенты: Смартавиа, Nordwind, Utair, СмартАвиа (8 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: S7 Engineering | Запросы ТУЗ+EXP: 17 · клиенты: S7 Engineering, Смартавиа, Nordwind, Utair (8 уник.)</t>
         </is>
       </c>
       <c r="L5" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 8 — Смартавиа, Nordwind, Utair, СмартАвиа, Якутия, qty≈44). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (17 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — S7 Engineering, qty≈1); запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 8 — S7 Engineering, Смартавиа, Nordwind, Utair, СмартАвиа, qty≈42.4118). Сопоставление: ALT P/N, точное P/N. На складе: 17 шт. (17 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $1,720.00: медиана продажных цен ТАЗ (все даты) (n=1, min $1,720.00, max $1,720.00, последний заказ 2025-02-25). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (511 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       <c r="H6" s="10" t="n">
         <v>124</v>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9297,7 +9297,7 @@
       <c r="H7" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9351,7 +9351,7 @@
       <c r="H8" s="10" t="n">
         <v>1370</v>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9405,7 +9405,7 @@
       <c r="H9" s="16" t="n">
         <v>750</v>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9459,7 +9459,7 @@
       <c r="H10" s="10" t="n">
         <v>196</v>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9513,7 +9513,7 @@
       <c r="H11" s="16" t="n">
         <v>651</v>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9567,7 +9567,7 @@
       <c r="H12" s="10" t="n">
         <v>1038</v>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9621,7 +9621,7 @@
       <c r="H13" s="16" t="n">
         <v>3375</v>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9675,7 +9675,7 @@
       <c r="H14" s="10" t="n">
         <v>1680</v>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9729,7 +9729,7 @@
       <c r="H15" s="16" t="n">
         <v>72</v>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9783,7 +9783,7 @@
       <c r="H16" s="10" t="n">
         <v>284</v>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9837,7 +9837,7 @@
       <c r="H17" s="16" t="n">
         <v>28524</v>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9891,7 +9891,7 @@
       <c r="H18" s="10" t="n">
         <v>1900</v>
       </c>
-      <c r="I18" s="18" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -9945,7 +9945,7 @@
       <c r="H19" s="16" t="n">
         <v>1170</v>
       </c>
-      <c r="I19" s="18" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -9999,7 +9999,7 @@
       <c r="H20" s="10" t="n">
         <v>5190</v>
       </c>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10053,7 +10053,7 @@
       <c r="H21" s="16" t="n">
         <v>7450</v>
       </c>
-      <c r="I21" s="18" t="inlineStr">
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10107,7 +10107,7 @@
       <c r="H22" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10161,7 +10161,7 @@
       <c r="H23" s="16" t="n">
         <v>2840</v>
       </c>
-      <c r="I23" s="18" t="inlineStr">
+      <c r="I23" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10215,7 +10215,7 @@
       <c r="H24" s="10" t="n">
         <v>1910</v>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I24" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10269,7 +10269,7 @@
       <c r="H25" s="16" t="n">
         <v>2500</v>
       </c>
-      <c r="I25" s="18" t="inlineStr">
+      <c r="I25" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10323,7 +10323,7 @@
       <c r="H26" s="10" t="n">
         <v>670</v>
       </c>
-      <c r="I26" s="18" t="inlineStr">
+      <c r="I26" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10377,7 +10377,7 @@
       <c r="H27" s="16" t="n">
         <v>530</v>
       </c>
-      <c r="I27" s="18" t="inlineStr">
+      <c r="I27" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10431,7 +10431,7 @@
       <c r="H28" s="10" t="n">
         <v>2632</v>
       </c>
-      <c r="I28" s="18" t="inlineStr">
+      <c r="I28" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10485,7 +10485,7 @@
       <c r="H29" s="16" t="n">
         <v>4320</v>
       </c>
-      <c r="I29" s="18" t="inlineStr">
+      <c r="I29" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10539,7 +10539,7 @@
       <c r="H30" s="10" t="n">
         <v>1600</v>
       </c>
-      <c r="I30" s="18" t="inlineStr">
+      <c r="I30" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10593,7 +10593,7 @@
       <c r="H31" s="16" t="n">
         <v>440</v>
       </c>
-      <c r="I31" s="18" t="inlineStr">
+      <c r="I31" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10647,7 +10647,7 @@
       <c r="H32" s="10" t="n">
         <v>1080</v>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -10701,7 +10701,7 @@
       <c r="H33" s="16" t="n">
         <v>2800</v>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -10755,7 +10755,7 @@
       <c r="H34" s="10" t="n">
         <v>5100</v>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -10809,7 +10809,7 @@
       <c r="H35" s="16" t="n">
         <v>350</v>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I35" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="G37" s="13" t="n"/>
       <c r="H37" s="13" t="n"/>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -10963,7 +10963,7 @@
       <c r="H38" s="10" t="n">
         <v>620</v>
       </c>
-      <c r="I38" s="11" t="inlineStr">
+      <c r="I38" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="G39" s="13" t="n"/>
       <c r="H39" s="13" t="n"/>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I39" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11067,7 +11067,7 @@
       <c r="H40" s="10" t="n">
         <v>170.5</v>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I40" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11121,7 +11121,7 @@
       <c r="H41" s="16" t="n">
         <v>5422</v>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I41" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
-      <c r="I42" s="11" t="inlineStr">
+      <c r="I42" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11225,7 +11225,7 @@
       <c r="H43" s="16" t="n">
         <v>2050</v>
       </c>
-      <c r="I43" s="11" t="inlineStr">
+      <c r="I43" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="7" t="n"/>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="I44" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11329,7 +11329,7 @@
       <c r="H45" s="16" t="n">
         <v>8.4</v>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I45" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11383,7 +11383,7 @@
       <c r="H46" s="10" t="n">
         <v>190</v>
       </c>
-      <c r="I46" s="11" t="inlineStr">
+      <c r="I46" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="G47" s="13" t="n"/>
       <c r="H47" s="13" t="n"/>
-      <c r="I47" s="11" t="inlineStr">
+      <c r="I47" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="7" t="n"/>
-      <c r="I48" s="11" t="inlineStr">
+      <c r="I48" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11533,7 +11533,7 @@
       </c>
       <c r="G49" s="13" t="n"/>
       <c r="H49" s="13" t="n"/>
-      <c r="I49" s="11" t="inlineStr">
+      <c r="I49" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="7" t="n"/>
-      <c r="I50" s="11" t="inlineStr">
+      <c r="I50" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11633,7 +11633,7 @@
       </c>
       <c r="G51" s="13" t="n"/>
       <c r="H51" s="13" t="n"/>
-      <c r="I51" s="11" t="inlineStr">
+      <c r="I51" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11687,7 +11687,7 @@
       <c r="H52" s="10" t="n">
         <v>1500</v>
       </c>
-      <c r="I52" s="11" t="inlineStr">
+      <c r="I52" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11741,7 +11741,7 @@
       <c r="H53" s="16" t="n">
         <v>1020</v>
       </c>
-      <c r="I53" s="11" t="inlineStr">
+      <c r="I53" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11795,7 +11795,7 @@
       <c r="H54" s="10" t="n">
         <v>6375</v>
       </c>
-      <c r="I54" s="11" t="inlineStr">
+      <c r="I54" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11845,7 +11845,7 @@
       </c>
       <c r="G55" s="13" t="n"/>
       <c r="H55" s="13" t="n"/>
-      <c r="I55" s="11" t="inlineStr">
+      <c r="I55" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="7" t="n"/>
-      <c r="I56" s="11" t="inlineStr">
+      <c r="I56" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11949,7 +11949,7 @@
       <c r="H57" s="16" t="n">
         <v>23250</v>
       </c>
-      <c r="I57" s="11" t="inlineStr">
+      <c r="I57" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="7" t="n"/>
-      <c r="I58" s="11" t="inlineStr">
+      <c r="I58" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="G59" s="13" t="n"/>
       <c r="H59" s="13" t="n"/>
-      <c r="I59" s="11" t="inlineStr">
+      <c r="I59" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -19394,7 +19394,7 @@
       <c r="H2" s="10" t="n">
         <v>15000</v>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19448,7 +19448,7 @@
       <c r="H3" s="16" t="n">
         <v>13700</v>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19460,12 +19460,12 @@
       </c>
       <c r="K3" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 4 · клиенты: Ираэро, Руслайн, Дримджет (3 уник.) | Запросы ТУЗ+EXP: 12 · клиенты: ЮВТ, Руслайн, АК Тулпар, Тулпар Эйр (7 уник.)</t>
+          <t>Заказы ТАЗ: 4 · клиенты: Ираэро, Руслайн, Дримджет (3 уник.) | Запросы ТУЗ+EXP: 12 · клиенты: Тулпар Эйр, Ираэро, Руслайн, Тулпар Аэро (7 уник.)</t>
         </is>
       </c>
       <c r="L3" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 3 — Ираэро, Руслайн, Дримджет, qty≈4); запросов ТУЗ+EXP: 12 (уник. P/N+клиент+день; клиентов: 7 — ЮВТ, Руслайн, АК Тулпар, Тулпар Эйр, Ираэро, qty≈13). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $13,700.00: медиана продажных цен ТАЗ (все даты) (n=3, min $13,150.00, max $14,000.00, последний заказ 2025-09-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (300 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 3 — Ираэро, Руслайн, Дримджет, qty≈4); запросов ТУЗ+EXP: 12 (уник. P/N+клиент+день; клиентов: 7 — Тулпар Эйр, Ираэро, Руслайн, Тулпар Аэро, Аллюр Сервис, qty≈12.8). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $13,700.00: медиана продажных цен ТАЗ (все даты) (n=3, min $13,150.00, max $14,000.00, последний заказ 2025-09-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (300 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -19502,7 +19502,7 @@
       <c r="H4" s="10" t="n">
         <v>32800</v>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19556,7 +19556,7 @@
       <c r="H5" s="16" t="n">
         <v>101400</v>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19610,7 +19610,7 @@
       <c r="H6" s="10" t="n">
         <v>7600</v>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19664,7 +19664,7 @@
       <c r="H7" s="16" t="n">
         <v>17900</v>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19718,7 +19718,7 @@
       <c r="H8" s="10" t="n">
         <v>124200</v>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19772,7 +19772,7 @@
       <c r="H9" s="16" t="n">
         <v>18900</v>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19826,7 +19826,7 @@
       <c r="H10" s="10" t="n">
         <v>32000</v>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19880,7 +19880,7 @@
       <c r="H11" s="16" t="n">
         <v>15200</v>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19892,12 +19892,12 @@
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Тулпар Эйр | Запросы ТУЗ+EXP: 6 · клиенты: Скай Партнер, Ираэро, Ямал, Тулпар Эйр (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Тулпар Эйр | Запросы ТУЗ+EXP: 6 · клиенты: Ираэро, Ямал, Тулпар Эйр, Дримджет (5 уник.)</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Тулпар Эйр, qty≈1); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — Скай Партнер, Ираэро, Ямал, Тулпар Эйр, Дримджет, qty≈6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $15,200.00: медиана продажных цен ТАЗ (все даты) (n=1, min $15,200.00, max $15,200.00, последний заказ 2025-04-11). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (466 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Тулпар Эйр, qty≈1); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — Ираэро, Ямал, Тулпар Эйр, Дримджет, Скай Партнер, qty≈6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $15,200.00: медиана продажных цен ТАЗ (все даты) (n=1, min $15,200.00, max $15,200.00, последний заказ 2025-04-11). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (466 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -19934,7 +19934,7 @@
       <c r="H12" s="10" t="n">
         <v>8300</v>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -19988,7 +19988,7 @@
       <c r="H13" s="16" t="n">
         <v>1850</v>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -20042,7 +20042,7 @@
       <c r="H14" s="10" t="n">
         <v>8000</v>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -20096,7 +20096,7 @@
       <c r="H15" s="16" t="n">
         <v>12500</v>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -20150,7 +20150,7 @@
       <c r="H16" s="10" t="n">
         <v>30400</v>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -20204,7 +20204,7 @@
       <c r="H17" s="16" t="n">
         <v>7000</v>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -20258,7 +20258,7 @@
       <c r="H18" s="10" t="n">
         <v>34500</v>
       </c>
-      <c r="I18" s="18" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -20312,7 +20312,7 @@
       <c r="H19" s="16" t="n">
         <v>9700</v>
       </c>
-      <c r="I19" s="18" t="inlineStr">
+      <c r="I19" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -20339,17 +20339,17 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>B738</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>2LA006178-02</t>
+          <t>2612311-1</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>FLOODLIGHT UNIT-FIRST OFFICER</t>
+          <t>WHEEL ASSY - MLG</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -20358,32 +20358,32 @@
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>8450</v>
+        <v>7950</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>8450</v>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
+        <v>254400</v>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>средняя (заказы ТАЗ)</t>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Джет Экспресс | Запросы ТУЗ+EXP: 1 · клиенты: -</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Белавиа, S7, Аэрофлот (3 уник.)</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Джет Экспресс, qty≈1); запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — -, qty≈1). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $8,450.00: медиана продажных цен ТАЗ (все даты) (n=1, min $8,450.00, max $8,450.00, последний заказ 2023-03-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1215 дн. назад).</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Белавиа, S7, Аэрофлот, qty≈8). Сопоставление: точное P/N. На складе: 32 шт. (4 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $7,950.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=4, min $4,000.00, max $13,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-07.</t>
         </is>
       </c>
     </row>
@@ -20398,12 +20398,12 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>854D100-24</t>
+          <t>2LA006178-02</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>RIGHT WING OUTBOARD FLAP ACTUATOR</t>
+          <t>FLOODLIGHT UNIT-FIRST OFFICER</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -20415,29 +20415,29 @@
         <v>1</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>4600</v>
+        <v>8450</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>4600</v>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
+        <v>8450</v>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>средняя (предложения)</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Ямал (2 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Джет Экспресс | Запросы ТУЗ+EXP: 1 · клиенты: -</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — ЮВТ, Ямал, qty≈8). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $4,600.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $4,000.00, max $25,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-01.</t>
+          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Джет Экспресс, qty≈1); запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — -, qty≈1). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $8,450.00: медиана продажных цен ТАЗ (все даты) (n=1, min $8,450.00, max $8,450.00, последний заказ 2023-03-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1215 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -20452,12 +20452,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>S800-3000-00</t>
+          <t>854D100-24</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>RECORDER, FLIGHT DATA</t>
+          <t>RIGHT WING OUTBOARD FLAP ACTUATOR</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -20469,12 +20469,12 @@
         <v>1</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>16100</v>
+        <v>4600</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>16100</v>
-      </c>
-      <c r="I22" s="18" t="inlineStr">
+        <v>4600</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -20486,12 +20486,12 @@
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: Руслайн, Ираэро (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Ямал (2 уник.)</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — Руслайн, Ираэро, qty≈6). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,100.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $10,500.00, max $19,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-09.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — ЮВТ, Ямал, qty≈8). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $4,600.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $4,000.00, max $25,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-01.</t>
         </is>
       </c>
     </row>
@@ -20501,17 +20501,17 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>2612311-1</t>
+          <t>S800-3000-00</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>WHEEL ASSY - MLG</t>
+          <t>RECORDER, FLIGHT DATA</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -20520,17 +20520,17 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>11350</v>
+        <v>16100</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>363200</v>
+        <v>16100</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -20540,12 +20540,12 @@
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Белавиа, Аэрофлот (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: Ираэро, Руслайн (2 уник.)</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 2 — Белавиа, Аэрофлот, qty≈7). Сопоставление: точное P/N. На складе: 32 шт. (4 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $11,350.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=2, min $9,700.00, max $13,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-05-20.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — Ираэро, Руслайн, qty≈6). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,100.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $10,500.00, max $19,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-09.</t>
         </is>
       </c>
     </row>
@@ -20582,7 +20582,7 @@
       <c r="H24" s="10" t="n">
         <v>7800</v>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -20636,7 +20636,7 @@
       <c r="H25" s="16" t="n">
         <v>184500</v>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -20690,7 +20690,7 @@
       <c r="H26" s="10" t="n">
         <v>8270</v>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I26" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -20744,7 +20744,7 @@
       <c r="H27" s="16" t="n">
         <v>6550</v>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -20794,7 +20794,7 @@
       </c>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -20844,7 +20844,7 @@
       </c>
       <c r="G29" s="13" t="n"/>
       <c r="H29" s="13" t="n"/>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="7" t="n"/>
-      <c r="I30" s="11" t="inlineStr">
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -20948,7 +20948,7 @@
       <c r="H31" s="16" t="n">
         <v>19600</v>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -20998,7 +20998,7 @@
       </c>
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="7" t="n"/>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -21048,7 +21048,7 @@
       </c>
       <c r="G33" s="13" t="n"/>
       <c r="H33" s="13" t="n"/>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -21102,7 +21102,7 @@
       <c r="H34" s="10" t="n">
         <v>10450</v>
       </c>
-      <c r="I34" s="11" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -21152,7 +21152,7 @@
       </c>
       <c r="G35" s="13" t="n"/>
       <c r="H35" s="13" t="n"/>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I35" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="7" t="n"/>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -21256,7 +21256,7 @@
       <c r="H37" s="16" t="n">
         <v>5000</v>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="G38" s="7" t="n"/>
       <c r="H38" s="7" t="n"/>
-      <c r="I38" s="11" t="inlineStr">
+      <c r="I38" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -21360,7 +21360,7 @@
       <c r="H39" s="16" t="n">
         <v>5400</v>
       </c>
-      <c r="I39" s="11" t="inlineStr">
+      <c r="I39" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -21414,7 +21414,7 @@
       <c r="H40" s="10" t="n">
         <v>4150</v>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I40" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -22809,7 +22809,7 @@
       <c r="H2" s="10" t="n">
         <v>543.2</v>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -22821,12 +22821,12 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Руслайн, Русджет (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: Аллюр Сервис, Северо-Запад, Ямал, S7 Engineering (13 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Русджет, Дримджет, ЮВТ (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: АК Тулпар, Северо-Запад, Аллюр Сервис, Русджет (13 уник.)</t>
         </is>
       </c>
       <c r="L2" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Руслайн, Русджет, Дримджет, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — Аллюр Сервис, Северо-Запад, Ямал, S7 Engineering, Азимут, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — Руслайн, Русджет, Дримджет, ЮВТ, Тулпар Техник, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — АК Тулпар, Северо-Запад, Аллюр Сервис, Русджет, Тулпар Техник, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -22863,7 +22863,7 @@
       <c r="H3" s="16" t="n">
         <v>330</v>
       </c>
-      <c r="I3" s="17" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -22917,7 +22917,7 @@
       <c r="H4" s="10" t="n">
         <v>3050</v>
       </c>
-      <c r="I4" s="17" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -22929,12 +22929,12 @@
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 6 · клиенты: АК Тулпар (Джет Экспресс), ЛТ Сервис, Глобал Скай, Тулпар Эйр (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Глобал Скай, Тулпар Эйр, Ираэро, Руслайн (7 уник.)</t>
+          <t>Заказы ТАЗ: 6 · клиенты: Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс) (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн (7 уник.)</t>
         </is>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — АК Тулпар (Джет Экспресс), ЛТ Сервис, Глобал Скай, Тулпар Эйр, Руслайн, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Глобал Скай, Тулпар Эйр, Ираэро, Руслайн, ТАРП Авиэйшн, qty≈26.25). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс), ЛТ Сервис, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн, Ямал, qty≈26.6667). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
         </is>
       </c>
     </row>
@@ -22971,7 +22971,7 @@
       <c r="H5" s="16" t="n">
         <v>798</v>
       </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23025,7 +23025,7 @@
       <c r="H6" s="10" t="n">
         <v>256</v>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23079,7 +23079,7 @@
       <c r="H7" s="16" t="n">
         <v>340</v>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23133,7 +23133,7 @@
       <c r="H8" s="10" t="n">
         <v>49200</v>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23187,7 +23187,7 @@
       <c r="H9" s="16" t="n">
         <v>101400</v>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23241,7 +23241,7 @@
       <c r="H10" s="10" t="n">
         <v>3800</v>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23295,7 +23295,7 @@
       <c r="H11" s="16" t="n">
         <v>2610</v>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23349,7 +23349,7 @@
       <c r="H12" s="10" t="n">
         <v>587.8</v>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23403,7 +23403,7 @@
       <c r="H13" s="16" t="n">
         <v>1.55</v>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23457,7 +23457,7 @@
       <c r="H14" s="10" t="n">
         <v>10.9</v>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23511,7 +23511,7 @@
       <c r="H15" s="16" t="n">
         <v>42205.5</v>
       </c>
-      <c r="I15" s="17" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23565,7 +23565,7 @@
       <c r="H16" s="10" t="n">
         <v>19566.5</v>
       </c>
-      <c r="I16" s="17" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23577,12 +23577,12 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: Ираэро, Джет Экспресс (2 уник.) | Запросы ТУЗ+EXP: 11 · клиенты: Дримджет, Руслайн, ЮВТ, Ираэро (4 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: Ираэро, Джет Экспресс (2 уник.) | Запросы ТУЗ+EXP: 11 · клиенты: Руслайн, Дримджет, ЮВТ, Ираэро (4 уник.)</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 2 — Ираэро, Джет Экспресс, qty≈2); запросов ТУЗ+EXP: 11 (уник. P/N+клиент+день; клиентов: 4 — Дримджет, Руслайн, ЮВТ, Ираэро, qty≈13). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $19,566.50: медиана продажных цен ТАЗ (все даты) (n=2, min $11,800.00, max $27,333.00, последний заказ 2025-09-19). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (305 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 2 — Ираэро, Джет Экспресс, qty≈2); запросов ТУЗ+EXP: 11 (уник. P/N+клиент+день; клиентов: 4 — Руслайн, Дримджет, ЮВТ, Ираэро, qty≈13). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $19,566.50: медиана продажных цен ТАЗ (все даты) (n=2, min $11,800.00, max $27,333.00, последний заказ 2025-09-19). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (305 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -23619,7 +23619,7 @@
       <c r="H17" s="16" t="n">
         <v>6200</v>
       </c>
-      <c r="I17" s="17" t="inlineStr">
+      <c r="I17" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23673,7 +23673,7 @@
       <c r="H18" s="10" t="n">
         <v>1800</v>
       </c>
-      <c r="I18" s="17" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -23700,51 +23700,51 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>979998-3</t>
+          <t>38E93-6</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>VALVE, BLEED, SHUTOFF, ISOLATION</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>OH, R</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="F19" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>16500</v>
+        <v>4100</v>
       </c>
       <c r="H19" s="16" t="n">
-        <v>33000</v>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
+        <v>4100</v>
+      </c>
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>средняя (заказы ТАЗ)</t>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: МБК-С | Запросы ТУЗ+EXP: 8 · клиенты: АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал (6 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 8 · клиенты: Белавиа, Аэрофлот, S7 Engineering, S7 (6 уник.)</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — МБК-С, qty≈2); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 6 — АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал, Тулпар Эйр, qty≈8). Сопоставление: точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: OVERHAULED; REPAIRED / BER?. Ориентир $16,500.00: медиана продажных цен ТАЗ (все даты) (n=1, min $16,500.00, max $16,500.00, последний заказ 2023-03-02). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1237 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 6 — Белавиа, Аэрофлот, S7 Engineering, S7, АК Сибирь, qty≈12.4). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
         </is>
       </c>
     </row>
@@ -23754,51 +23754,51 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>0727540</t>
+          <t>979998-3</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>SHROUD</t>
+          <t>VALVE, BLEED, SHUTOFF, ISOLATION</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>OH, R</t>
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>500</v>
+        <v>16500</v>
       </c>
       <c r="H20" s="10" t="n">
-        <v>500</v>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
+        <v>33000</v>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
-        <is>
-          <t>низкая (предложения)</t>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: Nordwind, Уральские Авиалинии, -, Аэрофлот (7 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: МБК-С | Запросы ТУЗ+EXP: 8 · клиенты: АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал (6 уник.)</t>
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Nordwind, Уральские Авиалинии, -, Аэрофлот, АК Россия, qty≈94). Сопоставление: ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $500.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=7, min $260.00, max $5,700.00, последнее предложение 2025-01-30). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 537 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — МБК-С, qty≈2); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 6 — АК Тулпар (Джет Экспресс), Дримджет, Скай Партнер, Ямал, Тулпар Эйр, qty≈8). Сопоставление: точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: OVERHAULED; REPAIRED / BER?. Ориентир $16,500.00: медиана продажных цен ТАЗ (все даты) (n=1, min $16,500.00, max $16,500.00, последний заказ 2023-03-02). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1237 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -23813,12 +23813,12 @@
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>ABS0604-4</t>
+          <t>0727540</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>WASHER</t>
+          <t>SHROUD</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -23827,32 +23827,32 @@
         </is>
       </c>
       <c r="F21" s="15" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>3</v>
+        <v>500</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>150</v>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
+        <v>500</v>
+      </c>
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>средняя (заказы ТАЗ)</t>
+      <c r="J21" s="19" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: VDT | Запросы ТУЗ+EXP: 8 · клиенты: Ямал, S7 Engineering, VDT, Аэрофлот Техникс (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: Nordwind, Уральские Авиалинии, -, Аэрофлот (7 уник.)</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — VDT, qty≈170); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 4 — Ямал, S7 Engineering, VDT, Аэрофлот Техникс, qty≈1236). Сопоставление: точное P/N. На складе: 50 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3.00: медиана продажных цен ТАЗ (все даты) (n=1, min $3.00, max $3.00, последний заказ 2024-11-22). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (606 дн. назад).</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Nordwind, Уральские Авиалинии, -, Аэрофлот, АК Россия, qty≈94). Сопоставление: ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $500.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=7, min $260.00, max $5,700.00, последнее предложение 2025-01-30). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 537 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -23862,51 +23862,51 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>979998-1</t>
+          <t>ABS0604-4</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>VALVE, SHUTOFF, PRESSURE REGULATING</t>
+          <t>WASHER</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F22" s="9" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>12300</v>
+        <v>3</v>
       </c>
       <c r="H22" s="10" t="n">
-        <v>24600</v>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
+        <v>150</v>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>средняя (предложения)</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 17 · клиенты: ЮВТ, Ямал, Скай Партнер, Аллюр Сервис (6 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: VDT | Запросы ТУЗ+EXP: 8 · клиенты: Ямал, S7 Engineering, VDT, Аэрофлот Техникс (4 уник.)</t>
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 6 — ЮВТ, Ямал, Скай Партнер, Аллюр Сервис, Дримджет, qty≈18). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $12,300.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=11, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — VDT, qty≈170); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 4 — Ямал, S7 Engineering, VDT, Аэрофлот Техникс, qty≈1236). Сопоставление: точное P/N. На складе: 50 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3.00: медиана продажных цен ТАЗ (все даты) (n=1, min $3.00, max $3.00, последний заказ 2024-11-22). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (606 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -23916,51 +23916,51 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>737MAX</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>P2-07-0021-002</t>
+          <t>979998-1</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>BATTERY</t>
+          <t>VALVE, SHUTOFF, PRESSURE REGULATING</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>SV</t>
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G23" s="16" t="n">
-        <v>98</v>
+        <v>12300</v>
       </c>
       <c r="H23" s="16" t="n">
-        <v>686</v>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
+        <v>24600</v>
+      </c>
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J23" s="20" t="inlineStr">
-        <is>
-          <t>высокая (заказы ТАЗ)</t>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: 407 Техникс | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Белавиа, S7 Engineering, Победа (5 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 17 · клиенты: ЮВТ, Руслайн, Ямал, Скай Партнер (6 уник.)</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — 407 Техникс, qty≈16); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — ЮВТ, Белавиа, S7 Engineering, Победа, ВТС ДЖЕТС, qty≈122). Сопоставление: точное P/N. На складе: 7 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $98.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $98.00, max $98.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-16).</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 6 — ЮВТ, Руслайн, Ямал, Скай Партнер, Аллюр Сервис, qty≈18). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $12,300.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=11, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -23970,34 +23970,34 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>737MAX</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>38E93-6</t>
+          <t>P2-07-0021-002</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>FILTER</t>
+          <t>BATTERY</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>SV</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>4100</v>
+        <v>98</v>
       </c>
       <c r="H24" s="10" t="n">
-        <v>4100</v>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
+        <v>686</v>
+      </c>
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 7 · клиенты: Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: 407 Техникс | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Белавиа, S7 Engineering, Победа (5 уник.)</t>
         </is>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 7 (уник. P/N+клиент+день; клиентов: 5 — Белавиа, АК Сибирь, S7 Engineering, Уральские Авиалинии, Аэрофлот, qty≈11.5). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — 407 Техникс, qty≈16); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — ЮВТ, Белавиа, S7 Engineering, Победа, ВТС ДЖЕТС, qty≈122). Сопоставление: точное P/N. На складе: 7 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $98.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $98.00, max $98.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-16).</t>
         </is>
       </c>
     </row>
@@ -24051,7 +24051,7 @@
       <c r="H25" s="16" t="n">
         <v>14300</v>
       </c>
-      <c r="I25" s="17" t="inlineStr">
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24105,7 +24105,7 @@
       <c r="H26" s="10" t="n">
         <v>56700</v>
       </c>
-      <c r="I26" s="17" t="inlineStr">
+      <c r="I26" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24159,7 +24159,7 @@
       <c r="H27" s="16" t="n">
         <v>264</v>
       </c>
-      <c r="I27" s="17" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24171,12 +24171,12 @@
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: АК Тулпар, Авиасервис, ЮВТ, Дримджет (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Авиасервис, Дримджет, АК Тулпар (4 уник.)</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — АК Тулпар, Авиасервис, ЮВТ, Дримджет, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Авиасервис, Дримджет, АК Тулпар, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -24213,7 +24213,7 @@
       <c r="H28" s="10" t="n">
         <v>841.5</v>
       </c>
-      <c r="I28" s="17" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24267,7 +24267,7 @@
       <c r="H29" s="16" t="n">
         <v>44800</v>
       </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24321,7 +24321,7 @@
       <c r="H30" s="10" t="n">
         <v>505</v>
       </c>
-      <c r="I30" s="17" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24333,12 +24333,12 @@
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Ямал | Запросы ТУЗ+EXP: 4 · клиенты: Алроса, Ямал, СмартАвиа, Ай Флай (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Ямал | Запросы ТУЗ+EXP: 4 · клиенты: Ай Флай, Ямал, СмартАвиа, Алроса (4 уник.)</t>
         </is>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Ямал, qty≈50); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Алроса, Ямал, СмартАвиа, Ай Флай, qty≈63). Сопоставление: ALT P/N, точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $101.00: медиана продажных цен ТАЗ (все даты) (n=1, min $101.00, max $101.00, последний заказ 2024-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (721 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Ямал, qty≈50); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Ай Флай, Ямал, СмартАвиа, Алроса, qty≈63). Сопоставление: ALT P/N, точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $101.00: медиана продажных цен ТАЗ (все даты) (n=1, min $101.00, max $101.00, последний заказ 2024-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (721 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -24375,7 +24375,7 @@
       <c r="H31" s="16" t="n">
         <v>360.6</v>
       </c>
-      <c r="I31" s="17" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24429,7 +24429,7 @@
       <c r="H32" s="10" t="n">
         <v>60800</v>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24441,12 +24441,12 @@
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Тулпар Эйр | Запросы ТУЗ+EXP: 6 · клиенты: Скай Партнер, Ираэро, Ямал, Тулпар Эйр (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Тулпар Эйр | Запросы ТУЗ+EXP: 6 · клиенты: Ираэро, Ямал, Тулпар Эйр, Дримджет (5 уник.)</t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Тулпар Эйр, qty≈1); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — Скай Партнер, Ираэро, Ямал, Тулпар Эйр, Дримджет, qty≈6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 4 шт. (4 строк АТИ). Состояние склада: OVERHAULED; SERVICEABLE. Ориентир $15,200.00: медиана продажных цен ТАЗ (все даты) (n=1, min $15,200.00, max $15,200.00, последний заказ 2025-04-11). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (466 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Тулпар Эйр, qty≈1); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 5 — Ираэро, Ямал, Тулпар Эйр, Дримджет, Скай Партнер, qty≈6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 4 шт. (4 строк АТИ). Состояние склада: OVERHAULED; SERVICEABLE. Ориентир $15,200.00: медиана продажных цен ТАЗ (все даты) (n=1, min $15,200.00, max $15,200.00, последний заказ 2025-04-11). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (466 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -24483,7 +24483,7 @@
       <c r="H33" s="16" t="n">
         <v>402</v>
       </c>
-      <c r="I33" s="17" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24537,7 +24537,7 @@
       <c r="H34" s="10" t="n">
         <v>635</v>
       </c>
-      <c r="I34" s="17" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24591,7 +24591,7 @@
       <c r="H35" s="16" t="n">
         <v>23000</v>
       </c>
-      <c r="I35" s="17" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24645,7 +24645,7 @@
       <c r="H36" s="10" t="n">
         <v>200.48</v>
       </c>
-      <c r="I36" s="17" t="inlineStr">
+      <c r="I36" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24699,7 +24699,7 @@
       <c r="H37" s="16" t="n">
         <v>8300</v>
       </c>
-      <c r="I37" s="17" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24753,7 +24753,7 @@
       <c r="H38" s="10" t="n">
         <v>12120</v>
       </c>
-      <c r="I38" s="17" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24807,7 +24807,7 @@
       <c r="H39" s="16" t="n">
         <v>2670</v>
       </c>
-      <c r="I39" s="17" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24861,7 +24861,7 @@
       <c r="H40" s="10" t="n">
         <v>16380</v>
       </c>
-      <c r="I40" s="17" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24915,7 +24915,7 @@
       <c r="H41" s="16" t="n">
         <v>16000</v>
       </c>
-      <c r="I41" s="17" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -24969,7 +24969,7 @@
       <c r="H42" s="10" t="n">
         <v>21000</v>
       </c>
-      <c r="I42" s="17" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25023,7 +25023,7 @@
       <c r="H43" s="16" t="n">
         <v>9400</v>
       </c>
-      <c r="I43" s="17" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25077,7 +25077,7 @@
       <c r="H44" s="10" t="n">
         <v>9400</v>
       </c>
-      <c r="I44" s="17" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25131,7 +25131,7 @@
       <c r="H45" s="16" t="n">
         <v>75000</v>
       </c>
-      <c r="I45" s="17" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25185,7 +25185,7 @@
       <c r="H46" s="10" t="n">
         <v>2800</v>
       </c>
-      <c r="I46" s="17" t="inlineStr">
+      <c r="I46" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25239,7 +25239,7 @@
       <c r="H47" s="16" t="n">
         <v>346</v>
       </c>
-      <c r="I47" s="17" t="inlineStr">
+      <c r="I47" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25293,7 +25293,7 @@
       <c r="H48" s="10" t="n">
         <v>950</v>
       </c>
-      <c r="I48" s="17" t="inlineStr">
+      <c r="I48" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25347,7 +25347,7 @@
       <c r="H49" s="16" t="n">
         <v>306</v>
       </c>
-      <c r="I49" s="17" t="inlineStr">
+      <c r="I49" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25401,7 +25401,7 @@
       <c r="H50" s="10" t="n">
         <v>176000</v>
       </c>
-      <c r="I50" s="17" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25455,7 +25455,7 @@
       <c r="H51" s="16" t="n">
         <v>139.08</v>
       </c>
-      <c r="I51" s="17" t="inlineStr">
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25509,7 +25509,7 @@
       <c r="H52" s="10" t="n">
         <v>284</v>
       </c>
-      <c r="I52" s="17" t="inlineStr">
+      <c r="I52" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25563,7 +25563,7 @@
       <c r="H53" s="16" t="n">
         <v>70000</v>
       </c>
-      <c r="I53" s="17" t="inlineStr">
+      <c r="I53" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25617,7 +25617,7 @@
       <c r="H54" s="10" t="n">
         <v>1248</v>
       </c>
-      <c r="I54" s="17" t="inlineStr">
+      <c r="I54" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25629,12 +25629,12 @@
       </c>
       <c r="K54" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Nordwind, Северо-Запад, Аэрофлот, Аэрофлот Техникс (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Северо-Запад, Аэрофлот, Аэрофлот Техникс, Nordwind (4 уник.)</t>
         </is>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — Nordwind, Северо-Запад, Аэрофлот, Аэрофлот Техникс, qty≈129). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 6 шт. (2 строк АТИ). Состояние склада: NEW. Ориентир $208.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $120.00, max $270.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — Северо-Запад, Аэрофлот, Аэрофлот Техникс, Nordwind, qty≈129). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 6 шт. (2 строк АТИ). Состояние склада: NEW. Ориентир $208.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $120.00, max $270.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -25671,7 +25671,7 @@
       <c r="H55" s="16" t="n">
         <v>74400</v>
       </c>
-      <c r="I55" s="17" t="inlineStr">
+      <c r="I55" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25683,12 +25683,12 @@
       </c>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: ЛТ Сервис | Запросы ТУЗ+EXP: 3 · клиенты: ЮВТ, АК Тулпар, Ямал (3 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: ЛТ Сервис | Запросы ТУЗ+EXP: 3 · клиенты: Ямал, ЮВТ, АК Тулпар (3 уник.)</t>
         </is>
       </c>
       <c r="L55" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — ЛТ Сервис, qty≈1); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, АК Тулпар, Ямал, qty≈3). Сопоставление: ALT P/N, точное P/N. На складе: 6 шт. (6 строк АТИ). Состояние склада: REPAIRED / BER?; SERVICEABLE. Ориентир $12,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $12,400.00, max $12,400.00, последний заказ 2023-01-20). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1278 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — ЛТ Сервис, qty≈1); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Ямал, ЮВТ, АК Тулпар, qty≈3). Сопоставление: ALT P/N, точное P/N. На складе: 6 шт. (6 строк АТИ). Состояние склада: REPAIRED / BER?; SERVICEABLE. Ориентир $12,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $12,400.00, max $12,400.00, последний заказ 2023-01-20). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1278 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -25725,7 +25725,7 @@
       <c r="H56" s="10" t="n">
         <v>14000</v>
       </c>
-      <c r="I56" s="17" t="inlineStr">
+      <c r="I56" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25779,7 +25779,7 @@
       <c r="H57" s="16" t="n">
         <v>7850</v>
       </c>
-      <c r="I57" s="17" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25833,7 +25833,7 @@
       <c r="H58" s="10" t="n">
         <v>9800</v>
       </c>
-      <c r="I58" s="17" t="inlineStr">
+      <c r="I58" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25887,7 +25887,7 @@
       <c r="H59" s="16" t="n">
         <v>130.21</v>
       </c>
-      <c r="I59" s="17" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25941,7 +25941,7 @@
       <c r="H60" s="10" t="n">
         <v>48000</v>
       </c>
-      <c r="I60" s="17" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -25995,7 +25995,7 @@
       <c r="H61" s="16" t="n">
         <v>955</v>
       </c>
-      <c r="I61" s="17" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -26049,7 +26049,7 @@
       <c r="H62" s="10" t="n">
         <v>852.5</v>
       </c>
-      <c r="I62" s="17" t="inlineStr">
+      <c r="I62" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -26103,7 +26103,7 @@
       <c r="H63" s="16" t="n">
         <v>380</v>
       </c>
-      <c r="I63" s="18" t="inlineStr">
+      <c r="I63" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26157,7 +26157,7 @@
       <c r="H64" s="10" t="n">
         <v>2660</v>
       </c>
-      <c r="I64" s="18" t="inlineStr">
+      <c r="I64" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26211,7 +26211,7 @@
       <c r="H65" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="I65" s="18" t="inlineStr">
+      <c r="I65" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26265,7 +26265,7 @@
       <c r="H66" s="10" t="n">
         <v>1656</v>
       </c>
-      <c r="I66" s="18" t="inlineStr">
+      <c r="I66" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26319,7 +26319,7 @@
       <c r="H67" s="16" t="n">
         <v>630.5</v>
       </c>
-      <c r="I67" s="18" t="inlineStr">
+      <c r="I67" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26331,12 +26331,12 @@
       </c>
       <c r="K67" s="14" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Аэрофлот, Уральские Авиалинии, Utair, Победа (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Utair, Победа, Аэрофлот, Уральские Авиалинии (4 уник.)</t>
         </is>
       </c>
       <c r="L67" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Аэрофлот, Уральские Авиалинии, Utair, Победа, qty≈69). Сопоставление: ALT P/N, точное P/N. На складе: 13 шт. (2 строк АТИ). Состояние склада: NEW. Ориентир $48.50: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $48.00, max $49.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Utair, Победа, Аэрофлот, Уральские Авиалинии, qty≈69). Сопоставление: ALT P/N, точное P/N. На складе: 13 шт. (2 строк АТИ). Состояние склада: NEW. Ориентир $48.50: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $48.00, max $49.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -26373,7 +26373,7 @@
       <c r="H68" s="10" t="n">
         <v>308</v>
       </c>
-      <c r="I68" s="18" t="inlineStr">
+      <c r="I68" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26427,7 +26427,7 @@
       <c r="H69" s="16" t="n">
         <v>384</v>
       </c>
-      <c r="I69" s="18" t="inlineStr">
+      <c r="I69" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26481,7 +26481,7 @@
       <c r="H70" s="10" t="n">
         <v>426</v>
       </c>
-      <c r="I70" s="18" t="inlineStr">
+      <c r="I70" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26493,12 +26493,12 @@
       </c>
       <c r="K70" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Nordwind, Аэрофлот Техникс (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Аэрофлот Техникс, Nordwind (3 уник.)</t>
         </is>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Аэрофлот, Nordwind, Аэрофлот Техникс, qty≈115.25). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $213.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=6, min $127.00, max $310.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Аэрофлот, Аэрофлот Техникс, Nordwind, qty≈142). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $213.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=6, min $127.00, max $310.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -26535,7 +26535,7 @@
       <c r="H71" s="16" t="n">
         <v>2400</v>
       </c>
-      <c r="I71" s="18" t="inlineStr">
+      <c r="I71" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26547,12 +26547,12 @@
       </c>
       <c r="K71" s="14" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Азур Эйр | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Азур Эйр (2 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Азур Эйр | Запросы ТУЗ+EXP: 5 · клиенты: Азур Эйр, Аэрофлот (2 уник.)</t>
         </is>
       </c>
       <c r="L71" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Азур Эйр, qty≈2); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 2 — Аэрофлот, Азур Эйр, qty≈7). Сопоставление: ведущие нули, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,400.00, max $2,400.00, последний заказ 2024-01-12). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (921 дн. назад).</t>
+          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Азур Эйр, qty≈2); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 2 — Азур Эйр, Аэрофлот, qty≈7). Сопоставление: ведущие нули, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,400.00, max $2,400.00, последний заказ 2024-01-12). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (921 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -26589,7 +26589,7 @@
       <c r="H72" s="10" t="n">
         <v>4020</v>
       </c>
-      <c r="I72" s="18" t="inlineStr">
+      <c r="I72" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26643,7 +26643,7 @@
       <c r="H73" s="16" t="n">
         <v>1620</v>
       </c>
-      <c r="I73" s="18" t="inlineStr">
+      <c r="I73" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26697,7 +26697,7 @@
       <c r="H74" s="10" t="n">
         <v>100000</v>
       </c>
-      <c r="I74" s="18" t="inlineStr">
+      <c r="I74" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26751,7 +26751,7 @@
       <c r="H75" s="16" t="n">
         <v>111</v>
       </c>
-      <c r="I75" s="18" t="inlineStr">
+      <c r="I75" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26805,7 +26805,7 @@
       <c r="H76" s="10" t="n">
         <v>406</v>
       </c>
-      <c r="I76" s="18" t="inlineStr">
+      <c r="I76" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26859,7 +26859,7 @@
       <c r="H77" s="16" t="n">
         <v>24800</v>
       </c>
-      <c r="I77" s="18" t="inlineStr">
+      <c r="I77" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26871,12 +26871,12 @@
       </c>
       <c r="K77" s="14" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: Nordwind, S7 Engineering, Белавиа (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: Белавиа, Nordwind, S7 Engineering (3 уник.)</t>
         </is>
       </c>
       <c r="L77" s="14" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 3 — Nordwind, S7 Engineering, Белавиа, qty≈6). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: INSPECTED / TESTED?; SERVICEABLE. Ориентир $12,400.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=2, min $11,500.00, max $13,300.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-02.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 3 — Белавиа, Nordwind, S7 Engineering, qty≈6). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: INSPECTED / TESTED?; SERVICEABLE. Ориентир $12,400.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=2, min $11,500.00, max $13,300.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-02.</t>
         </is>
       </c>
     </row>
@@ -26913,7 +26913,7 @@
       <c r="H78" s="10" t="n">
         <v>6500</v>
       </c>
-      <c r="I78" s="18" t="inlineStr">
+      <c r="I78" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -26967,7 +26967,7 @@
       <c r="H79" s="16" t="n">
         <v>52</v>
       </c>
-      <c r="I79" s="18" t="inlineStr">
+      <c r="I79" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27021,7 +27021,7 @@
       <c r="H80" s="10" t="n">
         <v>9700</v>
       </c>
-      <c r="I80" s="18" t="inlineStr">
+      <c r="I80" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27075,7 +27075,7 @@
       <c r="H81" s="16" t="n">
         <v>2560</v>
       </c>
-      <c r="I81" s="18" t="inlineStr">
+      <c r="I81" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27129,7 +27129,7 @@
       <c r="H82" s="10" t="n">
         <v>1730</v>
       </c>
-      <c r="I82" s="18" t="inlineStr">
+      <c r="I82" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27183,7 +27183,7 @@
       <c r="H83" s="16" t="n">
         <v>18600</v>
       </c>
-      <c r="I83" s="18" t="inlineStr">
+      <c r="I83" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27237,7 +27237,7 @@
       <c r="H84" s="10" t="n">
         <v>11400</v>
       </c>
-      <c r="I84" s="18" t="inlineStr">
+      <c r="I84" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27291,7 +27291,7 @@
       <c r="H85" s="16" t="n">
         <v>40800</v>
       </c>
-      <c r="I85" s="18" t="inlineStr">
+      <c r="I85" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27345,7 +27345,7 @@
       <c r="H86" s="10" t="n">
         <v>17800</v>
       </c>
-      <c r="I86" s="18" t="inlineStr">
+      <c r="I86" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27399,7 +27399,7 @@
       <c r="H87" s="16" t="n">
         <v>1910</v>
       </c>
-      <c r="I87" s="18" t="inlineStr">
+      <c r="I87" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27453,7 +27453,7 @@
       <c r="H88" s="10" t="n">
         <v>35100</v>
       </c>
-      <c r="I88" s="18" t="inlineStr">
+      <c r="I88" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27507,7 +27507,7 @@
       <c r="H89" s="16" t="n">
         <v>670</v>
       </c>
-      <c r="I89" s="18" t="inlineStr">
+      <c r="I89" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27561,7 +27561,7 @@
       <c r="H90" s="10" t="n">
         <v>13200</v>
       </c>
-      <c r="I90" s="18" t="inlineStr">
+      <c r="I90" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27615,7 +27615,7 @@
       <c r="H91" s="16" t="n">
         <v>3050</v>
       </c>
-      <c r="I91" s="18" t="inlineStr">
+      <c r="I91" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27669,7 +27669,7 @@
       <c r="H92" s="10" t="n">
         <v>76</v>
       </c>
-      <c r="I92" s="18" t="inlineStr">
+      <c r="I92" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27723,7 +27723,7 @@
       <c r="H93" s="16" t="n">
         <v>56</v>
       </c>
-      <c r="I93" s="18" t="inlineStr">
+      <c r="I93" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27777,7 +27777,7 @@
       <c r="H94" s="10" t="n">
         <v>62</v>
       </c>
-      <c r="I94" s="18" t="inlineStr">
+      <c r="I94" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27831,7 +27831,7 @@
       <c r="H95" s="16" t="n">
         <v>10366.14</v>
       </c>
-      <c r="I95" s="18" t="inlineStr">
+      <c r="I95" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27885,7 +27885,7 @@
       <c r="H96" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="I96" s="18" t="inlineStr">
+      <c r="I96" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27935,7 +27935,7 @@
       </c>
       <c r="G97" s="13" t="n"/>
       <c r="H97" s="13" t="n"/>
-      <c r="I97" s="18" t="inlineStr">
+      <c r="I97" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -27989,7 +27989,7 @@
       <c r="H98" s="10" t="n">
         <v>4940</v>
       </c>
-      <c r="I98" s="18" t="inlineStr">
+      <c r="I98" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28043,7 +28043,7 @@
       <c r="H99" s="16" t="n">
         <v>3.2</v>
       </c>
-      <c r="I99" s="18" t="inlineStr">
+      <c r="I99" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28097,7 +28097,7 @@
       <c r="H100" s="10" t="n">
         <v>24920</v>
       </c>
-      <c r="I100" s="18" t="inlineStr">
+      <c r="I100" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28151,7 +28151,7 @@
       <c r="H101" s="16" t="n">
         <v>3420</v>
       </c>
-      <c r="I101" s="18" t="inlineStr">
+      <c r="I101" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28205,7 +28205,7 @@
       <c r="H102" s="10" t="n">
         <v>1950</v>
       </c>
-      <c r="I102" s="18" t="inlineStr">
+      <c r="I102" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28259,7 +28259,7 @@
       <c r="H103" s="16" t="n">
         <v>4500</v>
       </c>
-      <c r="I103" s="18" t="inlineStr">
+      <c r="I103" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28313,7 +28313,7 @@
       <c r="H104" s="10" t="n">
         <v>2800</v>
       </c>
-      <c r="I104" s="18" t="inlineStr">
+      <c r="I104" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28367,7 +28367,7 @@
       <c r="H105" s="16" t="n">
         <v>470</v>
       </c>
-      <c r="I105" s="18" t="inlineStr">
+      <c r="I105" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28421,7 +28421,7 @@
       <c r="H106" s="10" t="n">
         <v>1000</v>
       </c>
-      <c r="I106" s="18" t="inlineStr">
+      <c r="I106" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28475,7 +28475,7 @@
       <c r="H107" s="16" t="n">
         <v>46000</v>
       </c>
-      <c r="I107" s="18" t="inlineStr">
+      <c r="I107" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28529,7 +28529,7 @@
       <c r="H108" s="10" t="n">
         <v>550</v>
       </c>
-      <c r="I108" s="18" t="inlineStr">
+      <c r="I108" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28583,7 +28583,7 @@
       <c r="H109" s="16" t="n">
         <v>3.4</v>
       </c>
-      <c r="I109" s="18" t="inlineStr">
+      <c r="I109" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28637,7 +28637,7 @@
       <c r="H110" s="10" t="n">
         <v>5400</v>
       </c>
-      <c r="I110" s="18" t="inlineStr">
+      <c r="I110" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28691,7 +28691,7 @@
       <c r="H111" s="16" t="n">
         <v>180</v>
       </c>
-      <c r="I111" s="18" t="inlineStr">
+      <c r="I111" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28745,7 +28745,7 @@
       <c r="H112" s="10" t="n">
         <v>61950</v>
       </c>
-      <c r="I112" s="18" t="inlineStr">
+      <c r="I112" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28799,7 +28799,7 @@
       <c r="H113" s="16" t="n">
         <v>17600</v>
       </c>
-      <c r="I113" s="18" t="inlineStr">
+      <c r="I113" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28853,7 +28853,7 @@
       <c r="H114" s="10" t="n">
         <v>2500</v>
       </c>
-      <c r="I114" s="18" t="inlineStr">
+      <c r="I114" s="11" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -28907,7 +28907,7 @@
       <c r="H115" s="16" t="n">
         <v>5950</v>
       </c>
-      <c r="I115" s="11" t="inlineStr">
+      <c r="I115" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -28957,7 +28957,7 @@
       </c>
       <c r="G116" s="7" t="n"/>
       <c r="H116" s="7" t="n"/>
-      <c r="I116" s="11" t="inlineStr">
+      <c r="I116" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -28969,12 +28969,12 @@
       </c>
       <c r="K116" s="8" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: Северсталь, ЮВТ (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: ЮВТ, Северсталь (2 уник.)</t>
         </is>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 2 — Северсталь, ЮВТ, qty≈17). Сопоставление: ALT P/N, точное P/N. На складе: 3 шт. (3 строк АТИ). Состояние склада: NEW; SERVICEABLE. Ориентировочная цена не рассчитана: нет «Продажная, ед.» в ТАЗ и нет Offered/Sell Price в ТУЗ/EXP. ВНИМАНИЕ: спрос/заказы есть, но sell/offered цены нет — денежная оценка невозможна.</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 2 — ЮВТ, Северсталь, qty≈17). Сопоставление: ALT P/N, точное P/N. На складе: 3 шт. (3 строк АТИ). Состояние склада: NEW; SERVICEABLE. Ориентировочная цена не рассчитана: нет «Продажная, ед.» в ТАЗ и нет Offered/Sell Price в ТУЗ/EXP. ВНИМАНИЕ: спрос/заказы есть, но sell/offered цены нет — денежная оценка невозможна.</t>
         </is>
       </c>
     </row>
@@ -29007,7 +29007,7 @@
       </c>
       <c r="G117" s="13" t="n"/>
       <c r="H117" s="13" t="n"/>
-      <c r="I117" s="11" t="inlineStr">
+      <c r="I117" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29061,7 +29061,7 @@
       <c r="H118" s="10" t="n">
         <v>980</v>
       </c>
-      <c r="I118" s="11" t="inlineStr">
+      <c r="I118" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29115,7 +29115,7 @@
       <c r="H119" s="16" t="n">
         <v>416</v>
       </c>
-      <c r="I119" s="11" t="inlineStr">
+      <c r="I119" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29169,7 +29169,7 @@
       <c r="H120" s="10" t="n">
         <v>21400</v>
       </c>
-      <c r="I120" s="11" t="inlineStr">
+      <c r="I120" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29223,7 +29223,7 @@
       <c r="H121" s="16" t="n">
         <v>25600</v>
       </c>
-      <c r="I121" s="11" t="inlineStr">
+      <c r="I121" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29277,7 +29277,7 @@
       <c r="H122" s="10" t="n">
         <v>92400</v>
       </c>
-      <c r="I122" s="11" t="inlineStr">
+      <c r="I122" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29331,7 +29331,7 @@
       <c r="H123" s="16" t="n">
         <v>40600</v>
       </c>
-      <c r="I123" s="11" t="inlineStr">
+      <c r="I123" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29385,7 +29385,7 @@
       <c r="H124" s="10" t="n">
         <v>3700</v>
       </c>
-      <c r="I124" s="11" t="inlineStr">
+      <c r="I124" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29439,7 +29439,7 @@
       <c r="H125" s="16" t="n">
         <v>12300</v>
       </c>
-      <c r="I125" s="11" t="inlineStr">
+      <c r="I125" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29493,7 +29493,7 @@
       <c r="H126" s="10" t="n">
         <v>350</v>
       </c>
-      <c r="I126" s="11" t="inlineStr">
+      <c r="I126" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29547,7 +29547,7 @@
       <c r="H127" s="16" t="n">
         <v>1230</v>
       </c>
-      <c r="I127" s="11" t="inlineStr">
+      <c r="I127" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29597,7 +29597,7 @@
       </c>
       <c r="G128" s="7" t="n"/>
       <c r="H128" s="7" t="n"/>
-      <c r="I128" s="11" t="inlineStr">
+      <c r="I128" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29651,7 +29651,7 @@
       <c r="H129" s="16" t="n">
         <v>410</v>
       </c>
-      <c r="I129" s="11" t="inlineStr">
+      <c r="I129" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29705,7 +29705,7 @@
       <c r="H130" s="10" t="n">
         <v>86800</v>
       </c>
-      <c r="I130" s="11" t="inlineStr">
+      <c r="I130" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29759,7 +29759,7 @@
       <c r="H131" s="16" t="n">
         <v>207</v>
       </c>
-      <c r="I131" s="11" t="inlineStr">
+      <c r="I131" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29813,7 +29813,7 @@
       <c r="H132" s="10" t="n">
         <v>1040</v>
       </c>
-      <c r="I132" s="11" t="inlineStr">
+      <c r="I132" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29867,7 +29867,7 @@
       <c r="H133" s="16" t="n">
         <v>161</v>
       </c>
-      <c r="I133" s="11" t="inlineStr">
+      <c r="I133" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29921,7 +29921,7 @@
       <c r="H134" s="10" t="n">
         <v>168</v>
       </c>
-      <c r="I134" s="11" t="inlineStr">
+      <c r="I134" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -29975,7 +29975,7 @@
       <c r="H135" s="16" t="n">
         <v>37000</v>
       </c>
-      <c r="I135" s="11" t="inlineStr">
+      <c r="I135" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30029,7 +30029,7 @@
       <c r="H136" s="10" t="n">
         <v>47750</v>
       </c>
-      <c r="I136" s="11" t="inlineStr">
+      <c r="I136" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30083,7 +30083,7 @@
       <c r="H137" s="16" t="n">
         <v>12000</v>
       </c>
-      <c r="I137" s="11" t="inlineStr">
+      <c r="I137" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30137,7 +30137,7 @@
       <c r="H138" s="10" t="n">
         <v>13100</v>
       </c>
-      <c r="I138" s="11" t="inlineStr">
+      <c r="I138" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30191,7 +30191,7 @@
       <c r="H139" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="I139" s="11" t="inlineStr">
+      <c r="I139" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30245,7 +30245,7 @@
       <c r="H140" s="10" t="n">
         <v>4000</v>
       </c>
-      <c r="I140" s="11" t="inlineStr">
+      <c r="I140" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30295,7 +30295,7 @@
       </c>
       <c r="G141" s="13" t="n"/>
       <c r="H141" s="13" t="n"/>
-      <c r="I141" s="11" t="inlineStr">
+      <c r="I141" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30345,7 +30345,7 @@
       </c>
       <c r="G142" s="7" t="n"/>
       <c r="H142" s="7" t="n"/>
-      <c r="I142" s="11" t="inlineStr">
+      <c r="I142" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30399,7 +30399,7 @@
       <c r="H143" s="16" t="n">
         <v>12350</v>
       </c>
-      <c r="I143" s="11" t="inlineStr">
+      <c r="I143" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30453,7 +30453,7 @@
       <c r="H144" s="10" t="n">
         <v>620</v>
       </c>
-      <c r="I144" s="11" t="inlineStr">
+      <c r="I144" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30507,7 +30507,7 @@
       <c r="H145" s="16" t="n">
         <v>4800</v>
       </c>
-      <c r="I145" s="11" t="inlineStr">
+      <c r="I145" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30561,7 +30561,7 @@
       <c r="H146" s="10" t="n">
         <v>22750</v>
       </c>
-      <c r="I146" s="11" t="inlineStr">
+      <c r="I146" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30615,7 +30615,7 @@
       <c r="H147" s="16" t="n">
         <v>2250</v>
       </c>
-      <c r="I147" s="11" t="inlineStr">
+      <c r="I147" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30665,7 +30665,7 @@
       </c>
       <c r="G148" s="7" t="n"/>
       <c r="H148" s="7" t="n"/>
-      <c r="I148" s="11" t="inlineStr">
+      <c r="I148" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30719,7 +30719,7 @@
       <c r="H149" s="16" t="n">
         <v>86294.39999999999</v>
       </c>
-      <c r="I149" s="11" t="inlineStr">
+      <c r="I149" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30773,7 +30773,7 @@
       <c r="H150" s="10" t="n">
         <v>990</v>
       </c>
-      <c r="I150" s="11" t="inlineStr">
+      <c r="I150" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30827,7 +30827,7 @@
       <c r="H151" s="16" t="n">
         <v>315</v>
       </c>
-      <c r="I151" s="11" t="inlineStr">
+      <c r="I151" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30877,7 +30877,7 @@
       </c>
       <c r="G152" s="7" t="n"/>
       <c r="H152" s="7" t="n"/>
-      <c r="I152" s="11" t="inlineStr">
+      <c r="I152" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30927,7 +30927,7 @@
       </c>
       <c r="G153" s="13" t="n"/>
       <c r="H153" s="13" t="n"/>
-      <c r="I153" s="11" t="inlineStr">
+      <c r="I153" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -30977,7 +30977,7 @@
       </c>
       <c r="G154" s="7" t="n"/>
       <c r="H154" s="7" t="n"/>
-      <c r="I154" s="11" t="inlineStr">
+      <c r="I154" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31031,7 +31031,7 @@
       <c r="H155" s="16" t="n">
         <v>13500</v>
       </c>
-      <c r="I155" s="11" t="inlineStr">
+      <c r="I155" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31085,7 +31085,7 @@
       <c r="H156" s="10" t="n">
         <v>67900</v>
       </c>
-      <c r="I156" s="11" t="inlineStr">
+      <c r="I156" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31135,7 +31135,7 @@
       </c>
       <c r="G157" s="13" t="n"/>
       <c r="H157" s="13" t="n"/>
-      <c r="I157" s="11" t="inlineStr">
+      <c r="I157" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31189,7 +31189,7 @@
       <c r="H158" s="10" t="n">
         <v>47100</v>
       </c>
-      <c r="I158" s="11" t="inlineStr">
+      <c r="I158" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31243,7 +31243,7 @@
       <c r="H159" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="I159" s="11" t="inlineStr">
+      <c r="I159" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31297,7 +31297,7 @@
       <c r="H160" s="10" t="n">
         <v>12480</v>
       </c>
-      <c r="I160" s="11" t="inlineStr">
+      <c r="I160" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31351,7 +31351,7 @@
       <c r="H161" s="16" t="n">
         <v>6480</v>
       </c>
-      <c r="I161" s="11" t="inlineStr">
+      <c r="I161" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31401,7 +31401,7 @@
       </c>
       <c r="G162" s="7" t="n"/>
       <c r="H162" s="7" t="n"/>
-      <c r="I162" s="11" t="inlineStr">
+      <c r="I162" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31451,7 +31451,7 @@
       </c>
       <c r="G163" s="13" t="n"/>
       <c r="H163" s="13" t="n"/>
-      <c r="I163" s="11" t="inlineStr">
+      <c r="I163" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31505,7 +31505,7 @@
       <c r="H164" s="10" t="n">
         <v>900</v>
       </c>
-      <c r="I164" s="11" t="inlineStr">
+      <c r="I164" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31559,7 +31559,7 @@
       <c r="H165" s="16" t="n">
         <v>2940</v>
       </c>
-      <c r="I165" s="11" t="inlineStr">
+      <c r="I165" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31613,7 +31613,7 @@
       <c r="H166" s="10" t="n">
         <v>1020</v>
       </c>
-      <c r="I166" s="11" t="inlineStr">
+      <c r="I166" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31667,7 +31667,7 @@
       <c r="H167" s="16" t="n">
         <v>2940</v>
       </c>
-      <c r="I167" s="11" t="inlineStr">
+      <c r="I167" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31717,7 +31717,7 @@
       </c>
       <c r="G168" s="7" t="n"/>
       <c r="H168" s="7" t="n"/>
-      <c r="I168" s="11" t="inlineStr">
+      <c r="I168" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31771,7 +31771,7 @@
       <c r="H169" s="16" t="n">
         <v>24800</v>
       </c>
-      <c r="I169" s="11" t="inlineStr">
+      <c r="I169" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31825,7 +31825,7 @@
       <c r="H170" s="10" t="n">
         <v>1960</v>
       </c>
-      <c r="I170" s="11" t="inlineStr">
+      <c r="I170" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31875,7 +31875,7 @@
       </c>
       <c r="G171" s="13" t="n"/>
       <c r="H171" s="13" t="n"/>
-      <c r="I171" s="11" t="inlineStr">
+      <c r="I171" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31925,7 +31925,7 @@
       </c>
       <c r="G172" s="7" t="n"/>
       <c r="H172" s="7" t="n"/>
-      <c r="I172" s="11" t="inlineStr">
+      <c r="I172" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -31979,7 +31979,7 @@
       <c r="H173" s="16" t="n">
         <v>22500</v>
       </c>
-      <c r="I173" s="11" t="inlineStr">
+      <c r="I173" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32029,7 +32029,7 @@
       </c>
       <c r="G174" s="7" t="n"/>
       <c r="H174" s="7" t="n"/>
-      <c r="I174" s="11" t="inlineStr">
+      <c r="I174" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32083,7 +32083,7 @@
       <c r="H175" s="16" t="n">
         <v>7200</v>
       </c>
-      <c r="I175" s="11" t="inlineStr">
+      <c r="I175" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32133,7 +32133,7 @@
       </c>
       <c r="G176" s="7" t="n"/>
       <c r="H176" s="7" t="n"/>
-      <c r="I176" s="11" t="inlineStr">
+      <c r="I176" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32187,7 +32187,7 @@
       <c r="H177" s="16" t="n">
         <v>37</v>
       </c>
-      <c r="I177" s="11" t="inlineStr">
+      <c r="I177" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32237,7 +32237,7 @@
       </c>
       <c r="G178" s="7" t="n"/>
       <c r="H178" s="7" t="n"/>
-      <c r="I178" s="11" t="inlineStr">
+      <c r="I178" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32291,7 +32291,7 @@
       <c r="H179" s="16" t="n">
         <v>11700</v>
       </c>
-      <c r="I179" s="11" t="inlineStr">
+      <c r="I179" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32345,7 +32345,7 @@
       <c r="H180" s="10" t="n">
         <v>154500</v>
       </c>
-      <c r="I180" s="11" t="inlineStr">
+      <c r="I180" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32395,7 +32395,7 @@
       </c>
       <c r="G181" s="13" t="n"/>
       <c r="H181" s="13" t="n"/>
-      <c r="I181" s="11" t="inlineStr">
+      <c r="I181" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32449,7 +32449,7 @@
       <c r="H182" s="10" t="n">
         <v>10120</v>
       </c>
-      <c r="I182" s="11" t="inlineStr">
+      <c r="I182" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32499,7 +32499,7 @@
       </c>
       <c r="G183" s="13" t="n"/>
       <c r="H183" s="13" t="n"/>
-      <c r="I183" s="11" t="inlineStr">
+      <c r="I183" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32549,7 +32549,7 @@
       </c>
       <c r="G184" s="7" t="n"/>
       <c r="H184" s="7" t="n"/>
-      <c r="I184" s="11" t="inlineStr">
+      <c r="I184" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32603,7 +32603,7 @@
       <c r="H185" s="16" t="n">
         <v>23200</v>
       </c>
-      <c r="I185" s="11" t="inlineStr">
+      <c r="I185" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32653,7 +32653,7 @@
       </c>
       <c r="G186" s="7" t="n"/>
       <c r="H186" s="7" t="n"/>
-      <c r="I186" s="11" t="inlineStr">
+      <c r="I186" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="G187" s="13" t="n"/>
       <c r="H187" s="13" t="n"/>
-      <c r="I187" s="11" t="inlineStr">
+      <c r="I187" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32753,7 +32753,7 @@
       </c>
       <c r="G188" s="7" t="n"/>
       <c r="H188" s="7" t="n"/>
-      <c r="I188" s="11" t="inlineStr">
+      <c r="I188" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32807,7 +32807,7 @@
       <c r="H189" s="16" t="n">
         <v>9340</v>
       </c>
-      <c r="I189" s="11" t="inlineStr">
+      <c r="I189" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32861,7 +32861,7 @@
       <c r="H190" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="I190" s="11" t="inlineStr">
+      <c r="I190" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32911,7 +32911,7 @@
       </c>
       <c r="G191" s="13" t="n"/>
       <c r="H191" s="13" t="n"/>
-      <c r="I191" s="11" t="inlineStr">
+      <c r="I191" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -32965,7 +32965,7 @@
       <c r="H192" s="10" t="n">
         <v>24820</v>
       </c>
-      <c r="I192" s="11" t="inlineStr">
+      <c r="I192" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33015,7 +33015,7 @@
       </c>
       <c r="G193" s="13" t="n"/>
       <c r="H193" s="13" t="n"/>
-      <c r="I193" s="11" t="inlineStr">
+      <c r="I193" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33069,7 +33069,7 @@
       <c r="H194" s="10" t="n">
         <v>6600</v>
       </c>
-      <c r="I194" s="11" t="inlineStr">
+      <c r="I194" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33119,7 +33119,7 @@
       </c>
       <c r="G195" s="13" t="n"/>
       <c r="H195" s="13" t="n"/>
-      <c r="I195" s="11" t="inlineStr">
+      <c r="I195" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33173,7 +33173,7 @@
       <c r="H196" s="10" t="n">
         <v>42300</v>
       </c>
-      <c r="I196" s="11" t="inlineStr">
+      <c r="I196" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33227,7 +33227,7 @@
       <c r="H197" s="16" t="n">
         <v>12000</v>
       </c>
-      <c r="I197" s="11" t="inlineStr">
+      <c r="I197" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33277,7 +33277,7 @@
       </c>
       <c r="G198" s="7" t="n"/>
       <c r="H198" s="7" t="n"/>
-      <c r="I198" s="11" t="inlineStr">
+      <c r="I198" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33327,7 +33327,7 @@
       </c>
       <c r="G199" s="13" t="n"/>
       <c r="H199" s="13" t="n"/>
-      <c r="I199" s="11" t="inlineStr">
+      <c r="I199" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33381,7 +33381,7 @@
       <c r="H200" s="10" t="n">
         <v>4865</v>
       </c>
-      <c r="I200" s="11" t="inlineStr">
+      <c r="I200" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33435,7 +33435,7 @@
       <c r="H201" s="16" t="n">
         <v>34000</v>
       </c>
-      <c r="I201" s="11" t="inlineStr">
+      <c r="I201" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33485,7 +33485,7 @@
       </c>
       <c r="G202" s="7" t="n"/>
       <c r="H202" s="7" t="n"/>
-      <c r="I202" s="11" t="inlineStr">
+      <c r="I202" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33539,7 +33539,7 @@
       <c r="H203" s="16" t="n">
         <v>7800</v>
       </c>
-      <c r="I203" s="11" t="inlineStr">
+      <c r="I203" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33593,7 +33593,7 @@
       <c r="H204" s="10" t="n">
         <v>6100</v>
       </c>
-      <c r="I204" s="11" t="inlineStr">
+      <c r="I204" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33647,7 +33647,7 @@
       <c r="H205" s="16" t="n">
         <v>4670</v>
       </c>
-      <c r="I205" s="11" t="inlineStr">
+      <c r="I205" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33701,7 +33701,7 @@
       <c r="H206" s="10" t="n">
         <v>4580</v>
       </c>
-      <c r="I206" s="11" t="inlineStr">
+      <c r="I206" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33751,7 +33751,7 @@
       </c>
       <c r="G207" s="13" t="n"/>
       <c r="H207" s="13" t="n"/>
-      <c r="I207" s="11" t="inlineStr">
+      <c r="I207" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33801,7 +33801,7 @@
       </c>
       <c r="G208" s="7" t="n"/>
       <c r="H208" s="7" t="n"/>
-      <c r="I208" s="11" t="inlineStr">
+      <c r="I208" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33851,7 +33851,7 @@
       </c>
       <c r="G209" s="13" t="n"/>
       <c r="H209" s="13" t="n"/>
-      <c r="I209" s="11" t="inlineStr">
+      <c r="I209" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33905,7 +33905,7 @@
       <c r="H210" s="10" t="n">
         <v>4150</v>
       </c>
-      <c r="I210" s="11" t="inlineStr">
+      <c r="I210" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -33955,7 +33955,7 @@
       </c>
       <c r="G211" s="13" t="n"/>
       <c r="H211" s="13" t="n"/>
-      <c r="I211" s="11" t="inlineStr">
+      <c r="I211" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -34009,7 +34009,7 @@
       <c r="H212" s="10" t="n">
         <v>5235</v>
       </c>
-      <c r="I212" s="11" t="inlineStr">
+      <c r="I212" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -34063,7 +34063,7 @@
       <c r="H213" s="16" t="n">
         <v>6400</v>
       </c>
-      <c r="I213" s="11" t="inlineStr">
+      <c r="I213" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -34113,7 +34113,7 @@
       </c>
       <c r="G214" s="7" t="n"/>
       <c r="H214" s="7" t="n"/>
-      <c r="I214" s="11" t="inlineStr">
+      <c r="I214" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
